--- a/src/attributions/attributions_saliency_traj_397.xlsx
+++ b/src/attributions/attributions_saliency_traj_397.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03162527084350586</v>
+        <v>0.0004978302749805152</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03772843256592751</v>
+        <v>9.273039904655889e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0846656933426857</v>
+        <v>0.0002143214514944702</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1292395293712616</v>
+        <v>0.0001663960429141298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07263222336769104</v>
+        <v>5.665477146976627e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2428677678108215</v>
+        <v>8.323558722622693e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1702333390712738</v>
+        <v>4.500771683524363e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4784181714057922</v>
+        <v>4.036538302898407e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3597369790077209</v>
+        <v>5.914111534366384e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.284789115190506</v>
+        <v>0.0005163208697922528</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1368962228298187</v>
+        <v>2.051887713605538e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07560399919748306</v>
+        <v>0.0001621944538783282</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1772844940423965</v>
+        <v>0.0001372694387100637</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3064974844455719</v>
+        <v>0.0003630715364124626</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2107135504484177</v>
+        <v>3.107036536675878e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2260793894529343</v>
+        <v>6.070389281376265e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2776677012443542</v>
+        <v>0.0001023656222969294</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5660790801048279</v>
+        <v>7.524526154156774e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1290021687746048</v>
+        <v>6.278933142311871e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02351228706538677</v>
+        <v>2.691598638193682e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1340437978506088</v>
+        <v>5.68649593333248e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2865612506866455</v>
+        <v>1.351577884634025e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.164735734462738</v>
+        <v>8.953229553299025e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2465027272701263</v>
+        <v>6.946396024432033e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2942613065242767</v>
+        <v>3.253172508266289e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.09942542761564255</v>
+        <v>7.694480882491916e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.08273147791624069</v>
+        <v>3.564637518138625e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1488257348537445</v>
+        <v>9.637670154916123e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2839697003364563</v>
+        <v>1.182557934953365e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.01884934678673744</v>
+        <v>1.337035791948438e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2549032270908356</v>
+        <v>0.0001258137344848365</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2119777202606201</v>
+        <v>6.775801739422604e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0703820213675499</v>
+        <v>0.0002119425917044282</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.03256139159202576</v>
+        <v>2.412862886558287e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1625416874885559</v>
+        <v>2.327885158592835e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.4257380962371826</v>
+        <v>1.493293166276999e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1923496276140213</v>
+        <v>4.386475484352559e-05</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1539847999811172</v>
+        <v>7.206863665487617e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1106684431433678</v>
+        <v>0.0001230160414706916</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.3180931210517883</v>
+        <v>0.0001032994186971337</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08310089260339737</v>
+        <v>5.118754779687151e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.114115871489048</v>
+        <v>4.534048912319122e-06</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0977105051279068</v>
+        <v>7.910930435173213e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1034400910139084</v>
+        <v>2.82914552371949e-05</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.2568266689777374</v>
+        <v>3.976849984610453e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.3517713844776154</v>
+        <v>0.0001713494420982897</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.06160084158182144</v>
+        <v>0.0001087696073227562</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.100477322936058</v>
+        <v>6.421086436603218e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2908612787723541</v>
+        <v>0.0001249038759851828</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.6389579176902771</v>
+        <v>0.0002820291556417942</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.08609262108802795</v>
+        <v>7.669666956644505e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1680410504341125</v>
+        <v>2.586243135738187e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.3860239684581757</v>
+        <v>4.540716327028349e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1443049609661102</v>
+        <v>5.786932524642907e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.3511412143707275</v>
+        <v>0.0001182227206300013</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.009272973984479904</v>
+        <v>6.12456860835664e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.2287115454673767</v>
+        <v>0.000100691060652025</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2550393044948578</v>
+        <v>0.0001091403537429869</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1203426793217659</v>
+        <v>0.0001623192802071571</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.2260375171899796</v>
+        <v>4.106550932192476e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.2438261806964874</v>
+        <v>4.685951716965064e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5885513424873352</v>
+        <v>1.589041676197667e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.4112167358398438</v>
+        <v>5.969229459878989e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1387028992176056</v>
+        <v>0.0002043257700279355</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1438082158565521</v>
+        <v>2.702552046685014e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1073866710066795</v>
+        <v>2.301433050888591e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.03523540869355202</v>
+        <v>5.523017171071842e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3237792551517487</v>
+        <v>8.80324932950316e-06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.07081658393144608</v>
+        <v>2.932110146502964e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2720748484134674</v>
+        <v>3.74141673091799e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.006838507950305939</v>
+        <v>5.290090120979585e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1423170566558838</v>
+        <v>2.951644273707643e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.2746007144451141</v>
+        <v>0.0001401444460498169</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.007674155756831169</v>
+        <v>2.05942469619913e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.05638847872614861</v>
+        <v>0.0001503858366049826</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.005010370165109634</v>
+        <v>8.328469266416505e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.04164232313632965</v>
+        <v>7.487089897040278e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0214359275996685</v>
+        <v>3.742104308912531e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1321785897016525</v>
+        <v>5.617913120659068e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1002960354089737</v>
+        <v>5.944749136688188e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.09560999274253845</v>
+        <v>7.073644519550726e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.01779894530773163</v>
+        <v>0.0001103909889934584</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.132215142250061</v>
+        <v>3.168094553984702e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.01708032190799713</v>
+        <v>3.370454578544013e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.03292274847626686</v>
+        <v>5.296667950460687e-05</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0655248835682869</v>
+        <v>3.785588341997936e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0481133796274662</v>
+        <v>1.276171815334237e-06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.01825269311666489</v>
+        <v>1.125366725318599e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.07569809257984161</v>
+        <v>4.381236522021936e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.07818291336297989</v>
+        <v>3.39251664627227e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.04688097536563873</v>
+        <v>6.284930350375362e-06</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1270141005516052</v>
+        <v>7.024651858955622e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.08476541191339493</v>
+        <v>8.943982538767159e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.03296168893575668</v>
+        <v>4.647738387575373e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.2672815322875977</v>
+        <v>9.452634549234062e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1054653599858284</v>
+        <v>8.630707452539355e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1468823850154877</v>
+        <v>7.935262146929745e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.007496215403079987</v>
+        <v>6.313144695013762e-05</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1572223007678986</v>
+        <v>3.236588963773102e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.009429074823856354</v>
+        <v>0.000100045173894614</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1136866360902786</v>
+        <v>4.539904330158606e-05</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.01366875972598791</v>
+        <v>5.883747144252993e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.08604976534843445</v>
+        <v>5.369108112063259e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.009885881096124649</v>
+        <v>1.193916614283808e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.006683114916086197</v>
+        <v>1.567930485180113e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.01344452053308487</v>
+        <v>1.536216041131411e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.05353251099586487</v>
+        <v>6.018201929691713e-06</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.06578657031059265</v>
+        <v>1.862019416876137e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.179532527923584</v>
+        <v>0.000122227895190008</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.4592058956623077</v>
+        <v>0.0004153874469920993</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.2537809908390045</v>
+        <v>5.833822797285393e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.09488028287887573</v>
+        <v>0.0001207906097988598</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.4142163395881653</v>
+        <v>2.084666084556375e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.6114807724952698</v>
+        <v>0.0002241313341073692</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.177513986825943</v>
+        <v>2.343714186281431e-05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1180986911058426</v>
+        <v>4.173242268734612e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.3363185524940491</v>
+        <v>9.829136251937598e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1623699367046356</v>
+        <v>4.771562817040831e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.004056801553815603</v>
+        <v>6.167520041344687e-05</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.1524288803339005</v>
+        <v>8.776080358074978e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.2524685561656952</v>
+        <v>8.17811960587278e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.4199417531490326</v>
+        <v>0.0001123800248024054</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09646087139844894</v>
+        <v>3.157064929837361e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0695076584815979</v>
+        <v>5.357595000532456e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.4124146103858948</v>
+        <v>6.652319279965013e-05</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.06189199537038803</v>
+        <v>7.816824108886067e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.007657818496227264</v>
+        <v>4.788797014043666e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.3427500128746033</v>
+        <v>6.005090108374134e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.06263824552297592</v>
+        <v>0.0002199699956690893</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.01447414513677359</v>
+        <v>7.330351218115538e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1682387888431549</v>
+        <v>0.0001494878815719858</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1463258564472198</v>
+        <v>4.428777538123541e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.05317425355315208</v>
+        <v>1.144699126598425e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0534832701086998</v>
+        <v>5.529046029550955e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.03921831399202347</v>
+        <v>5.175182013772428e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.05914308503270149</v>
+        <v>0.0001172531337942928</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1225694492459297</v>
+        <v>2.224736999778543e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.02534383349120617</v>
+        <v>6.460440999944694e-07</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.000973002053797245</v>
+        <v>5.214256088947877e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.09665876626968384</v>
+        <v>2.702184247027617e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1128817498683929</v>
+        <v>8.75670593813993e-06</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.02308573573827744</v>
+        <v>1.924719981616363e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.03479168564081192</v>
+        <v>7.782135980960447e-06</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02066291123628616</v>
+        <v>2.196599052695092e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.1388169676065445</v>
+        <v>8.995790994958952e-05</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1140539795160294</v>
+        <v>7.116846973076463e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.06765859574079514</v>
+        <v>6.30163231107872e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.1644273698329926</v>
+        <v>4.167576116742566e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.08196963369846344</v>
+        <v>8.689111382409465e-06</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.06204117834568024</v>
+        <v>0.0001297903945669532</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.007176883518695831</v>
+        <v>5.712737038265914e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.03688505664467812</v>
+        <v>3.574883157853037e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.04027898982167244</v>
+        <v>7.301627192646265e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0474071092903614</v>
+        <v>0.0001040200004354119</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1345186978578568</v>
+        <v>7.566509157186374e-05</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.002532759681344032</v>
+        <v>5.948512625764124e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.07131999731063843</v>
+        <v>4.813894702238031e-05</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01326289772987366</v>
+        <v>9.826555469771847e-06</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.007519763894379139</v>
+        <v>4.93905899929814e-05</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.01622699201107025</v>
+        <v>2.632601899676956e-05</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.1176319271326065</v>
+        <v>1.616169902263209e-05</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.1059758812189102</v>
+        <v>2.74655440080096e-06</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.05628740787506104</v>
+        <v>0.0002191948296967894</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.2839165925979614</v>
+        <v>3.555413422873244e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.1024135649204254</v>
+        <v>4.953452662448399e-05</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1711770743131638</v>
+        <v>5.274774230201729e-05</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.06967349350452423</v>
+        <v>3.027802631550003e-05</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1792202293872833</v>
+        <v>0.0001071534134098329</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.0178702101111412</v>
+        <v>8.174269169103354e-06</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2253352105617523</v>
+        <v>2.574511381681077e-05</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.01129080727696419</v>
+        <v>9.696183042251505e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1169391050934792</v>
+        <v>3.331858897581697e-05</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1126578971743584</v>
+        <v>3.708155782078393e-05</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1660869568586349</v>
+        <v>0.0001990464079426602</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.07220038026571274</v>
+        <v>0.0002848963194992393</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1886527985334396</v>
+        <v>9.169780241791159e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.3677631318569183</v>
+        <v>1.188761598314159e-05</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.06224904954433441</v>
+        <v>9.497729479335248e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.0004731416702270508</v>
+        <v>3.279702286818065e-05</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0005071312189102173</v>
+        <v>2.316934296686668e-05</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.007397320121526718</v>
+        <v>0.0001639721886022016</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.001028358936309814</v>
+        <v>3.297640796517953e-05</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1339389234781265</v>
+        <v>1.475813405704685e-05</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.2038869559764862</v>
+        <v>8.283406350528821e-05</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.03813127800822258</v>
+        <v>0.0001965125265996903</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1771626472473145</v>
+        <v>1.738183709676377e-05</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.05629214644432068</v>
+        <v>8.244113269029185e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.03107860311865807</v>
+        <v>7.979065412655473e-05</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.01541650667786598</v>
+        <v>3.247454515076242e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.001484310487285256</v>
+        <v>6.891419616295025e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.008668179623782635</v>
+        <v>0.0004479075432755053</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001452506548957899</v>
+        <v>3.802520222961903e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004304610192775726</v>
+        <v>0.0003309266758151352</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001329988008365035</v>
+        <v>0.0001746472989907488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001576371025294065</v>
+        <v>0.0001962698297575116</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002762774820439517</v>
+        <v>0.0001294054527534172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001673279621172696</v>
+        <v>9.118386515183374e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.611265517771244e-05</v>
+        <v>4.256098327459767e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002047281013801694</v>
+        <v>6.038255742168985e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005388274788856506</v>
+        <v>0.0005429168231785297</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003257568459957838</v>
+        <v>8.492686902172863e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003968197852373123</v>
+        <v>0.0004156468785367906</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00263300584629178</v>
+        <v>0.0002531518111936748</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003127713222056627</v>
+        <v>0.0001034461965900846</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005312899593263865</v>
+        <v>0.0001294705143664032</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001313456916250288</v>
+        <v>4.477375478018075e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007712588994763792</v>
+        <v>3.803669824264944e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.401081241667271e-07</v>
+        <v>2.267604577355087e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00112175103276968</v>
+        <v>2.479055183357559e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000453781511168927</v>
+        <v>4.738383722724393e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001113560050725937</v>
+        <v>1.723331934044836e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00017257769650314</v>
+        <v>3.080338137806393e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>2.926727756857872e-05</v>
+        <v>5.076131492387503e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00139780854806304</v>
+        <v>1.542629797768313e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004997144569642842</v>
+        <v>4.78580295748543e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0005420179222710431</v>
+        <v>9.861298894975334e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007310201763175428</v>
+        <v>5.981968934065662e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001425561145879328</v>
+        <v>2.444786878186278e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0001601177355041727</v>
+        <v>2.592700548120774e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0003278868971392512</v>
+        <v>2.213654079241678e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001141460845246911</v>
+        <v>9.024506289279088e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006331569165922701</v>
+        <v>5.05125499330461e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.555258106440306e-05</v>
+        <v>1.701202927506529e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.000582616834435612</v>
+        <v>2.014752681134269e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0005864003906026483</v>
+        <v>4.462407105165767e-06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0007384820492006838</v>
+        <v>9.706205673865043e-06</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0007256260141730309</v>
+        <v>0.0001056254841387272</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.580897439154796e-05</v>
+        <v>3.799158002948388e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0005191301461309195</v>
+        <v>5.735254671890289e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.000565224327147007</v>
+        <v>3.222070972697111e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001265541068278253</v>
+        <v>7.263512816280127e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0003094147832598537</v>
+        <v>3.970110265072435e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0004478695918805897</v>
+        <v>2.495366788934916e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0004869454132858664</v>
+        <v>9.033679816639051e-06</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0009279458317905664</v>
+        <v>6.405192834790796e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.005773164331912994</v>
+        <v>0.0003257385105825961</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0006573439459316432</v>
+        <v>6.846027099527419e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001636322122067213</v>
+        <v>0.0001724426401779056</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001291359192691743</v>
+        <v>0.0002301572822034359</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0001540992234367877</v>
+        <v>3.216893310309388e-05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0007326297927647829</v>
+        <v>3.162528628308792e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0006228039273992181</v>
+        <v>2.964853047160432e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.001140775391831994</v>
+        <v>2.560445864219218e-07</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0008005014387890697</v>
+        <v>3.896828275173903e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001099766348488629</v>
+        <v>5.620939919026569e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0009943586774170399</v>
+        <v>8.730096305953339e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0006653486052528024</v>
+        <v>4.417859599925578e-06</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.00218521011993289</v>
+        <v>1.213929317600559e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0009600330959074199</v>
+        <v>7.170798926381394e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0006656541954725981</v>
+        <v>2.344755375816021e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001057240646332502</v>
+        <v>9.269353904528543e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0001649821933824569</v>
+        <v>4.118883225601166e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001078226137906313</v>
+        <v>3.251403904869221e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0002817300555761904</v>
+        <v>6.164413207443431e-06</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0004331140662543476</v>
+        <v>3.415301034692675e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001172630931250751</v>
+        <v>7.53282438381575e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0008952982607297599</v>
+        <v>9.300126112066209e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0001207629247801378</v>
+        <v>2.034035969700199e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0002313257718924433</v>
+        <v>2.114244807671639e-06</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0002313116565346718</v>
+        <v>2.284050970047247e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0002953002403955907</v>
+        <v>2.631115421536379e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0004106467240490019</v>
+        <v>1.77095462277066e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003008515806868672</v>
+        <v>0.0001961751695489511</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.188911755889421e-05</v>
+        <v>4.982266545994207e-06</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.000469737482490018</v>
+        <v>0.0001152521144831553</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0003269679727964103</v>
+        <v>6.095927165006287e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.00133721309248358</v>
+        <v>3.735513382707722e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.000411126995459199</v>
+        <v>6.395592208718881e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0005797147750854492</v>
+        <v>1.547874126117676e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0005883335252292454</v>
+        <v>6.931106327101588e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0005765872774645686</v>
+        <v>5.178452738618944e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001535177696496248</v>
+        <v>0.0001272876834264025</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0004579409142024815</v>
+        <v>1.818268719944172e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0001718669518595561</v>
+        <v>9.413086081622168e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0001052731386153027</v>
+        <v>2.633293843246065e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0003443103632889688</v>
+        <v>4.341511521488428e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0003104078932665288</v>
+        <v>8.832405001157895e-06</v>
       </c>
       <c r="CK4" t="n">
-        <v>7.373288099188358e-05</v>
+        <v>1.390319994243328e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0002939882106147707</v>
+        <v>2.807555392791983e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0006224305252544582</v>
+        <v>4.463262303033844e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.144455745816231e-05</v>
+        <v>0.0001214520962093957</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001274112495593727</v>
+        <v>6.419264536816627e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001080684480257332</v>
+        <v>7.757030834909528e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001179318292997777</v>
+        <v>4.989212175132707e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0009298455552197993</v>
+        <v>5.447687726700678e-06</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0003690799931064248</v>
+        <v>1.34798947328818e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001663897186517715</v>
+        <v>5.420989327831194e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001564033882459626</v>
+        <v>4.274928505765274e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0005217929719947278</v>
+        <v>6.717869837302715e-06</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001176434685476124</v>
+        <v>0.0001402242196490988</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0004322109452914447</v>
+        <v>2.053083699138369e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0008127561304718256</v>
+        <v>0.0001076152402674779</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001126722490880638</v>
+        <v>3.819860648945905e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0004142821417190135</v>
+        <v>5.096446329844184e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0002612565003801137</v>
+        <v>1.562567194923759e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.208667865488678e-05</v>
+        <v>1.150981688624597e-06</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0002010792668443173</v>
+        <v>4.027368413517252e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0006265353295020759</v>
+        <v>5.223223706707358e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001156852813437581</v>
+        <v>9.095339919440448e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0003903041651938111</v>
+        <v>6.679454236291349e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002133964560925961</v>
+        <v>5.063018033979461e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001062180614098907</v>
+        <v>9.557445446262136e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.000156207664986141</v>
+        <v>0.0001505978143541142</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0005014413618482649</v>
+        <v>8.597031410317868e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.001023913966491818</v>
+        <v>0.0001138163061114028</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0001656076492508873</v>
+        <v>1.637611603655387e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001605214201845229</v>
+        <v>3.94688977394253e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0007682894356548786</v>
+        <v>8.111975330393761e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.000593498523812741</v>
+        <v>3.111351543338969e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>3.875000402331352e-05</v>
+        <v>3.978002132498659e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0001092606544261798</v>
+        <v>7.72037310525775e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001502359285950661</v>
+        <v>8.868360600899905e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.975579652935266e-05</v>
+        <v>5.763662920799106e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0001383689668728039</v>
+        <v>6.785710138501599e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0005116960965096951</v>
+        <v>0.000141069307574071</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0006223045638762414</v>
+        <v>9.349819265480619e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.006696927826852e-06</v>
+        <v>2.649637281137984e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001874085981398821</v>
+        <v>7.063338125590235e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003868882195092738</v>
+        <v>1.994599188037682e-06</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001023849006742239</v>
+        <v>2.972904985654168e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0001647685712669045</v>
+        <v>0.0001523741957498714</v>
       </c>
       <c r="EC4" t="n">
-        <v>4.963121318724006e-05</v>
+        <v>3.472143362159841e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0002714745060075074</v>
+        <v>0.0001877076574601233</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0002594263933133334</v>
+        <v>0.0001007107348414138</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0001314757391810417</v>
+        <v>1.102013266063295e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0006662821397185326</v>
+        <v>7.310269575100392e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0002398026990704238</v>
+        <v>2.495638364052866e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>8.022091060411185e-05</v>
+        <v>9.402172872796655e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0004288652853574604</v>
+        <v>3.887612183461897e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>8.680051541887224e-05</v>
+        <v>6.678057980025187e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0004436884773895144</v>
+        <v>1.383412381983362e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0004212943895254284</v>
+        <v>3.331069819978438e-07</v>
       </c>
       <c r="EN4" t="n">
-        <v>6.730170571245253e-05</v>
+        <v>1.692212754278444e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0009135121945291758</v>
+        <v>9.140676411334425e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001046384801156819</v>
+        <v>9.974408749258146e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.00036176762660034</v>
+        <v>3.568572356016375e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.001003514160402119</v>
+        <v>4.905807145405561e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.000599317136220634</v>
+        <v>4.31340595241636e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.002490937942638993</v>
+        <v>6.088898953748867e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>7.443776121363044e-05</v>
+        <v>1.381085166940466e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0005955220549367368</v>
+        <v>2.138518902938813e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0003922389587387443</v>
+        <v>6.967774970689788e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0004685358435381204</v>
+        <v>1.421206889062887e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001206289744004607</v>
+        <v>0.000139229727210477</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0002007590519497171</v>
+        <v>1.078612513083499e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0004833711427636445</v>
+        <v>9.387184400111437e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>1.873925793915987e-05</v>
+        <v>3.293723420938477e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0004943229723721743</v>
+        <v>5.449910531751812e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0002921510604210198</v>
+        <v>1.591148975421675e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.000058884732425e-05</v>
+        <v>2.104601480823476e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0002790605649352074</v>
+        <v>4.198259193799458e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0001397625601384789</v>
+        <v>2.383344963163836e-06</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0006468890933319926</v>
+        <v>7.020164775894955e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0004383305204100907</v>
+        <v>7.129610457923263e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0009821983985602856</v>
+        <v>6.479272269643843e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>1.016828173305839e-05</v>
+        <v>3.427343835937791e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0001840669719967991</v>
+        <v>8.460908429697156e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0004155065689701587</v>
+        <v>2.552465593907982e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0003456028643995523</v>
+        <v>4.671959322877228e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.001042642397806048</v>
+        <v>9.459303691983223e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.001050102990120649</v>
+        <v>9.039182259584777e-06</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001991718076169491</v>
+        <v>6.198592018336058e-06</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0001933574385475367</v>
+        <v>1.443358723918209e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.001819915138185024</v>
+        <v>0.0001210602422361262</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.003085345262661576</v>
+        <v>6.62156380712986e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0003314156201668084</v>
+        <v>7.072766311466694e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001810241228668019</v>
+        <v>1.901199721032754e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0008653440163470805</v>
+        <v>7.131918391678482e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0006618152838200331</v>
+        <v>9.495558333583176e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0008533507352694869</v>
+        <v>4.050039206049405e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0007678400143049657</v>
+        <v>9.268414578400552e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001089800032787025</v>
+        <v>6.387266330420971e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.000654515577480197</v>
+        <v>5.728318137698807e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.001068940153345466</v>
+        <v>0.0001508953719167039</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0007985644624568522</v>
+        <v>5.030658576288261e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.001291281543672085</v>
+        <v>7.595128408866003e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0004319859144743532</v>
+        <v>5.167151539353654e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0004176758229732513</v>
+        <v>2.812082857417408e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.010720527323429e-05</v>
+        <v>0.0005316939204931259</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0001917182671604678</v>
+        <v>0.001176254474557936</v>
       </c>
       <c r="C5" t="n">
-        <v>1.611439984117169e-05</v>
+        <v>0.000198229419765994</v>
       </c>
       <c r="D5" t="n">
-        <v>9.387127647642046e-05</v>
+        <v>0.0002529582707211375</v>
       </c>
       <c r="E5" t="n">
-        <v>8.816247282084078e-05</v>
+        <v>0.0002034093631664291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001000983684207313</v>
+        <v>0.0009771989425644279</v>
       </c>
       <c r="G5" t="n">
-        <v>1.414433427271433e-05</v>
+        <v>0.0001600545947439969</v>
       </c>
       <c r="H5" t="n">
-        <v>2.737040267675184e-05</v>
+        <v>0.000312332937028259</v>
       </c>
       <c r="I5" t="n">
-        <v>1.961224734259304e-05</v>
+        <v>0.0002174997352994978</v>
       </c>
       <c r="J5" t="n">
-        <v>1.386218900734093e-05</v>
+        <v>0.0005220847087912261</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001796166179701686</v>
+        <v>0.001349430764093995</v>
       </c>
       <c r="L5" t="n">
-        <v>3.064694465138018e-05</v>
+        <v>0.0002754746237769723</v>
       </c>
       <c r="M5" t="n">
-        <v>8.913591591408476e-05</v>
+        <v>5.357449481380172e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001184580469271168</v>
+        <v>0.0004001350025646389</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000126878687296994</v>
+        <v>0.0009753472986631095</v>
       </c>
       <c r="P5" t="n">
-        <v>3.370738704688847e-05</v>
+        <v>0.0001390550169162452</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.277629366493784e-05</v>
+        <v>7.600804383400828e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.000251697609201e-05</v>
+        <v>0.0003844829625450075</v>
       </c>
       <c r="S5" t="n">
-        <v>1.89688380487496e-05</v>
+        <v>0.0001673881342867389</v>
       </c>
       <c r="T5" t="n">
-        <v>4.791097308043391e-05</v>
+        <v>0.0002216590219177306</v>
       </c>
       <c r="U5" t="n">
-        <v>1.406801038683625e-05</v>
+        <v>0.0001976829953491688</v>
       </c>
       <c r="V5" t="n">
-        <v>4.270002136763651e-06</v>
+        <v>0.0003433763049542904</v>
       </c>
       <c r="W5" t="n">
-        <v>1.606553087185603e-05</v>
+        <v>0.0003138692118227482</v>
       </c>
       <c r="X5" t="n">
-        <v>4.144514605286531e-05</v>
+        <v>2.60680553765269e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.481721695512533e-06</v>
+        <v>5.30076285940595e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.863885912229307e-06</v>
+        <v>0.0001015671441564336</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.68229984815116e-06</v>
+        <v>7.561016536783427e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.268036041641608e-05</v>
+        <v>0.0002488198515493423</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.144355287076905e-05</v>
+        <v>0.0003545210929587483</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.775650086230598e-05</v>
+        <v>1.895304012577981e-05</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.465604484314099e-05</v>
+        <v>0.0005046592559665442</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.045798621315043e-05</v>
+        <v>0.0003128378884866834</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.754215554683469e-05</v>
+        <v>0.0001331373496213928</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.340413215686567e-05</v>
+        <v>4.957809142069891e-05</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.851424015825614e-06</v>
+        <v>0.0005224088090471923</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.351409966649953e-05</v>
+        <v>0.0001052483567036688</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.66403957438888e-06</v>
+        <v>3.334254506626166e-05</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.342111787991598e-05</v>
+        <v>0.0002440448442939669</v>
       </c>
       <c r="AM5" t="n">
-        <v>7.213706794573227e-06</v>
+        <v>0.0002419515221845359</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.037122976616956e-05</v>
+        <v>0.0002202563482569531</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.070550206350163e-05</v>
+        <v>0.0001013278233585879</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.707063686102629e-05</v>
+        <v>0.000177235939190723</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.839186552388128e-05</v>
+        <v>6.866430339869112e-05</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.064569823938655e-05</v>
+        <v>0.000206163531402126</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.966540134570096e-06</v>
+        <v>0.0001176648074761033</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.095499025424942e-05</v>
+        <v>0.000229404860874638</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0001271824148716405</v>
+        <v>0.001072988728992641</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.769800398207735e-06</v>
+        <v>0.0001499408099334687</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.019769428647123e-05</v>
+        <v>2.134591341018677e-06</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.683153459453024e-05</v>
+        <v>0.000224682007683441</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.15804133808706e-05</v>
+        <v>0.0005081085255369544</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.134754999540746e-05</v>
+        <v>9.511064854450524e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.318378963333089e-05</v>
+        <v>6.264704279601574e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.195412864442915e-05</v>
+        <v>9.225863323081285e-05</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.319150396739133e-05</v>
+        <v>7.620333781233057e-05</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.921421688981354e-05</v>
+        <v>4.614296631189063e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.340821083635092e-05</v>
+        <v>0.0001650995400268584</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.109438694082201e-05</v>
+        <v>0.0001223670842591673</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.000140785297844559</v>
+        <v>4.912266376777552e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.784751556348056e-05</v>
+        <v>0.000228046061238274</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.149122494505718e-05</v>
+        <v>0.0001135765487561002</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3.238252975279465e-05</v>
+        <v>0.0002545289171393961</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.368263201584341e-05</v>
+        <v>0.0001470126881031319</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.578019120846875e-05</v>
+        <v>4.832589183934033e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.068469934281893e-06</v>
+        <v>0.000290596712147817</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.868352228484582e-05</v>
+        <v>2.145660255337134e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.478644026065012e-05</v>
+        <v>4.515952605288476e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>8.26924224384129e-06</v>
+        <v>0.0002477437956258655</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.905609315144829e-05</v>
+        <v>0.00035493666655384</v>
       </c>
       <c r="BR5" t="n">
-        <v>3.148778341710567e-05</v>
+        <v>0.0003727077564690262</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.32012864924036e-05</v>
+        <v>2.306775968463626e-05</v>
       </c>
       <c r="BT5" t="n">
-        <v>2.885692993004341e-06</v>
+        <v>0.0002726276288740337</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.454984132782556e-05</v>
+        <v>3.512846888042986e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.057798939058557e-05</v>
+        <v>0.0008595956605859101</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.00540671357885e-05</v>
+        <v>0.000152561638969928</v>
       </c>
       <c r="BX5" t="n">
-        <v>2.642902290972415e-05</v>
+        <v>0.0002657595614437014</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.173011231818236e-06</v>
+        <v>0.0001039385970216244</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.121533725585323e-05</v>
+        <v>0.0003301750693935901</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.126888128055725e-05</v>
+        <v>0.0001828011882025748</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.941111223568441e-06</v>
+        <v>1.176218938780949e-05</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.723933559740544e-06</v>
+        <v>0.0001580778480274603</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.50378899788484e-07</v>
+        <v>0.0002824260445777327</v>
       </c>
       <c r="CE5" t="n">
-        <v>3.493060285109095e-05</v>
+        <v>0.0003159394254907966</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.604480766256529e-08</v>
+        <v>2.368146488151979e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>7.894763257354498e-06</v>
+        <v>0.000168950209626928</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.976939984160708e-06</v>
+        <v>0.0001602809352334589</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.336964214715408e-05</v>
+        <v>0.0002464128483552486</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.153742389054969e-05</v>
+        <v>0.0001195180375361815</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.615942437638296e-06</v>
+        <v>6.174576992634684e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>6.64367871650029e-06</v>
+        <v>1.911887011374347e-06</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.617159771034494e-05</v>
+        <v>6.826795288361609e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.732931716309395e-05</v>
+        <v>0.0005118627450428903</v>
       </c>
       <c r="CO5" t="n">
-        <v>5.703478791474481e-07</v>
+        <v>0.0001283886667806655</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.070433038170449e-05</v>
+        <v>5.775741010438651e-05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.189841350424103e-05</v>
+        <v>8.269998215837404e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>7.397029548883438e-06</v>
+        <v>3.647756602731533e-05</v>
       </c>
       <c r="CS5" t="n">
-        <v>5.273801798466593e-05</v>
+        <v>0.0002325016248505563</v>
       </c>
       <c r="CT5" t="n">
-        <v>6.940802995814011e-05</v>
+        <v>8.79954022821039e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.23917880046065e-05</v>
+        <v>0.0001798242592485622</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.031399278872414e-06</v>
+        <v>0.0002141100412700325</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.671654692676384e-05</v>
+        <v>0.0002633282856550068</v>
       </c>
       <c r="CX5" t="n">
-        <v>7.04840749676805e-06</v>
+        <v>7.50317849451676e-06</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.457684356864775e-05</v>
+        <v>0.0001674070081207901</v>
       </c>
       <c r="CZ5" t="n">
-        <v>4.413735041453037e-06</v>
+        <v>0.0001552044122945517</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.792015245882794e-05</v>
+        <v>0.0002329136477783322</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.566659011587035e-05</v>
+        <v>6.183917139424011e-05</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.652477749303216e-06</v>
+        <v>6.447110354201868e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>6.782508535252418e-06</v>
+        <v>2.105983185174409e-05</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.804745963658206e-05</v>
+        <v>6.706586282234639e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>4.93049701617565e-05</v>
+        <v>6.088164445827715e-05</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.126377825741656e-05</v>
+        <v>8.741080819163471e-05</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.985732524190098e-05</v>
+        <v>0.0002969513298012316</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.926590630318969e-05</v>
+        <v>0.0001920379290822893</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.943702955031767e-05</v>
+        <v>3.993796417489648e-05</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.32837225869298e-05</v>
+        <v>9.666325786383823e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.046457327902317e-05</v>
+        <v>0.0002900839608628303</v>
       </c>
       <c r="DM5" t="n">
-        <v>8.417482604272664e-06</v>
+        <v>0.0003011839871760458</v>
       </c>
       <c r="DN5" t="n">
-        <v>7.965140866872389e-06</v>
+        <v>1.886763493530452e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.07999821921112e-05</v>
+        <v>0.0002806108677759767</v>
       </c>
       <c r="DP5" t="n">
-        <v>3.824607574642869e-06</v>
+        <v>0.0001268268242711201</v>
       </c>
       <c r="DQ5" t="n">
-        <v>6.957484583836049e-05</v>
+        <v>0.000319496844895184</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.32001857511932e-05</v>
+        <v>5.652416439261287e-05</v>
       </c>
       <c r="DS5" t="n">
-        <v>3.784854925470427e-05</v>
+        <v>0.000135362206492573</v>
       </c>
       <c r="DT5" t="n">
-        <v>1.283716301259119e-05</v>
+        <v>6.481094169430435e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.207893546961714e-05</v>
+        <v>9.705902630230412e-05</v>
       </c>
       <c r="DV5" t="n">
-        <v>4.973576778866118e-06</v>
+        <v>0.0001623334974283352</v>
       </c>
       <c r="DW5" t="n">
-        <v>8.838031135383062e-06</v>
+        <v>0.0001106333584175445</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.916203291330021e-05</v>
+        <v>8.687822264619172e-05</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.444984940870199e-06</v>
+        <v>2.747145481407642e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.787282523466274e-05</v>
+        <v>1.43830657179933e-05</v>
       </c>
       <c r="EA5" t="n">
-        <v>7.493194971175399e-06</v>
+        <v>2.073950599879026e-05</v>
       </c>
       <c r="EB5" t="n">
-        <v>3.155041122226976e-05</v>
+        <v>0.0003181072243023664</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.943871913885232e-05</v>
+        <v>0.0001344628253718838</v>
       </c>
       <c r="ED5" t="n">
-        <v>4.175598951405846e-05</v>
+        <v>0.0001086334377760068</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.826161496865097e-05</v>
+        <v>0.000342171813827008</v>
       </c>
       <c r="EF5" t="n">
-        <v>7.358560651482549e-06</v>
+        <v>0.0002686080988496542</v>
       </c>
       <c r="EG5" t="n">
-        <v>2.544073868193664e-05</v>
+        <v>8.416667697019875e-06</v>
       </c>
       <c r="EH5" t="n">
-        <v>5.104902356833918e-06</v>
+        <v>5.105362652102485e-05</v>
       </c>
       <c r="EI5" t="n">
-        <v>4.84020056319423e-05</v>
+        <v>6.679014768451452e-05</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.42235257953871e-05</v>
+        <v>0.0002916087105404586</v>
       </c>
       <c r="EK5" t="n">
-        <v>1.914806489367038e-06</v>
+        <v>8.162301674019545e-05</v>
       </c>
       <c r="EL5" t="n">
-        <v>4.448432446224615e-05</v>
+        <v>6.869317076052539e-06</v>
       </c>
       <c r="EM5" t="n">
-        <v>5.929723556619138e-06</v>
+        <v>2.370128277107142e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>2.547510575823253e-06</v>
+        <v>5.047865852247924e-05</v>
       </c>
       <c r="EO5" t="n">
-        <v>5.317270733939949e-06</v>
+        <v>0.0001399046159349382</v>
       </c>
       <c r="EP5" t="n">
-        <v>3.059261644011713e-08</v>
+        <v>0.0001538636715849862</v>
       </c>
       <c r="EQ5" t="n">
-        <v>2.224266063421965e-05</v>
+        <v>6.388306792359799e-05</v>
       </c>
       <c r="ER5" t="n">
-        <v>1.82744552148506e-05</v>
+        <v>0.0002365413529332727</v>
       </c>
       <c r="ES5" t="n">
-        <v>3.000403921760153e-05</v>
+        <v>0.0003486181958578527</v>
       </c>
       <c r="ET5" t="n">
-        <v>5.48537791473791e-05</v>
+        <v>0.0002103808365063742</v>
       </c>
       <c r="EU5" t="n">
-        <v>7.792074939061422e-06</v>
+        <v>3.181336796842515e-05</v>
       </c>
       <c r="EV5" t="n">
-        <v>1.672129110374954e-05</v>
+        <v>0.0001537436619400978</v>
       </c>
       <c r="EW5" t="n">
-        <v>8.167799023794942e-07</v>
+        <v>0.0001678965054452419</v>
       </c>
       <c r="EX5" t="n">
-        <v>4.259417437424418e-06</v>
+        <v>0.0002919450053013861</v>
       </c>
       <c r="EY5" t="n">
-        <v>2.909917384386063e-05</v>
+        <v>0.0003217297489754856</v>
       </c>
       <c r="EZ5" t="n">
-        <v>1.01755324521946e-06</v>
+        <v>4.937171979690902e-06</v>
       </c>
       <c r="FA5" t="n">
-        <v>8.815721230348572e-06</v>
+        <v>0.0001557727664476261</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.020259787765099e-05</v>
+        <v>0.000201340124476701</v>
       </c>
       <c r="FC5" t="n">
-        <v>2.152607521566097e-05</v>
+        <v>0.0002030092873610556</v>
       </c>
       <c r="FD5" t="n">
-        <v>1.742044150887523e-05</v>
+        <v>0.000105722327134572</v>
       </c>
       <c r="FE5" t="n">
-        <v>3.277871883256012e-06</v>
+        <v>4.793524567503482e-05</v>
       </c>
       <c r="FF5" t="n">
-        <v>5.820073965878692e-06</v>
+        <v>0.0001036128378473222</v>
       </c>
       <c r="FG5" t="n">
-        <v>8.175437869795132e-06</v>
+        <v>0.0001552656176500022</v>
       </c>
       <c r="FH5" t="n">
-        <v>1.438495746697299e-05</v>
+        <v>0.0002103933511534706</v>
       </c>
       <c r="FI5" t="n">
-        <v>9.239910468750168e-06</v>
+        <v>4.189093306194991e-05</v>
       </c>
       <c r="FJ5" t="n">
-        <v>5.326182872522622e-05</v>
+        <v>0.0001843216305132955</v>
       </c>
       <c r="FK5" t="n">
-        <v>4.221976632834412e-05</v>
+        <v>4.601528780767694e-05</v>
       </c>
       <c r="FL5" t="n">
-        <v>2.041958396148402e-05</v>
+        <v>0.00027321872767061</v>
       </c>
       <c r="FM5" t="n">
-        <v>2.541555659263395e-05</v>
+        <v>0.000213947962038219</v>
       </c>
       <c r="FN5" t="n">
-        <v>5.027103907195851e-05</v>
+        <v>0.0004400003526825458</v>
       </c>
       <c r="FO5" t="n">
-        <v>1.136860919359606e-05</v>
+        <v>0.0001025455858325586</v>
       </c>
       <c r="FP5" t="n">
-        <v>3.002203811774962e-06</v>
+        <v>0.0002434957423247397</v>
       </c>
       <c r="FQ5" t="n">
-        <v>5.568120104726404e-05</v>
+        <v>0.0004993205657228827</v>
       </c>
       <c r="FR5" t="n">
-        <v>1.769712434906978e-05</v>
+        <v>0.0001254748203791678</v>
       </c>
       <c r="FS5" t="n">
-        <v>4.016072489321232e-05</v>
+        <v>4.252699909557123e-06</v>
       </c>
       <c r="FT5" t="n">
-        <v>1.945867552421987e-05</v>
+        <v>0.0001241998106706887</v>
       </c>
       <c r="FU5" t="n">
-        <v>4.686065221903846e-05</v>
+        <v>4.358034129836597e-05</v>
       </c>
       <c r="FV5" t="n">
-        <v>4.054322926094756e-05</v>
+        <v>5.93262302572839e-05</v>
       </c>
       <c r="FW5" t="n">
-        <v>1.490341855969746e-05</v>
+        <v>0.0003193528391420841</v>
       </c>
       <c r="FX5" t="n">
-        <v>3.440841828705743e-05</v>
+        <v>0.0003639021597336978</v>
       </c>
       <c r="FY5" t="n">
-        <v>1.803206032491289e-06</v>
+        <v>0.0002622612519189715</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.774750671756919e-05</v>
+        <v>2.084184779960196e-05</v>
       </c>
       <c r="GA5" t="n">
-        <v>5.216045974520966e-05</v>
+        <v>0.0001505705731688067</v>
       </c>
       <c r="GB5" t="n">
-        <v>2.380415025982074e-06</v>
+        <v>0.0003532150876708329</v>
       </c>
       <c r="GC5" t="n">
-        <v>1.310374500462785e-05</v>
+        <v>0.0001701348228380084</v>
       </c>
       <c r="GD5" t="n">
-        <v>1.954855360963847e-05</v>
+        <v>0.0002111580979544669</v>
       </c>
       <c r="GE5" t="n">
-        <v>7.987217941263225e-06</v>
+        <v>5.129641067469493e-08</v>
       </c>
       <c r="GF5" t="n">
-        <v>3.190949064446613e-05</v>
+        <v>7.58857058826834e-05</v>
       </c>
       <c r="GG5" t="n">
-        <v>1.260648605239112e-05</v>
+        <v>0.0003262386308051646</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.108266294002533</v>
+        <v>0.0001296245609410107</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6829075813293457</v>
+        <v>0.006827875971794128</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03999829292297363</v>
+        <v>0.002993891946971416</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2729755640029907</v>
+        <v>0.002473126631230116</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03466885536909103</v>
+        <v>0.001732106320559978</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1625585407018661</v>
+        <v>0.0009055536356754601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03027908690273762</v>
+        <v>0.002299776300787926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04594423249363899</v>
+        <v>0.001339875976555049</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02309314347803593</v>
+        <v>0.00121549260802567</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1594868749380112</v>
+        <v>0.0008312694262713194</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4562092125415802</v>
+        <v>0.00761920353397727</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02502814121544361</v>
+        <v>0.003243593033403158</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2494371086359024</v>
+        <v>0.004013181198388338</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1037666276097298</v>
+        <v>0.002483411924913526</v>
       </c>
       <c r="O7" t="n">
-        <v>0.240576446056366</v>
+        <v>0.001217799843288958</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03322049230337143</v>
+        <v>0.002271095756441355</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05559921264648438</v>
+        <v>0.0005277750315144658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03312055021524429</v>
+        <v>0.001116907922551036</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01306252554059029</v>
+        <v>0.0001430455013178289</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07333929836750031</v>
+        <v>0.0004962201928719878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01846401207149029</v>
+        <v>0.0005291561828926206</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09577526152133942</v>
+        <v>5.840977974003181e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0540880411863327</v>
+        <v>5.552963921218179e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05262987688183784</v>
+        <v>0.0006554491701535881</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07364099472761154</v>
+        <v>0.0006622120272368193</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06330788880586624</v>
+        <v>0.001081763301044703</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.06907882541418076</v>
+        <v>0.001947963843122125</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01315329596400261</v>
+        <v>0.000626255408860743</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0874456912279129</v>
+        <v>0.0001509019348304719</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01151209883391857</v>
+        <v>0.001280756201595068</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.04996777325868607</v>
+        <v>0.001006436534225941</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01178001146763563</v>
+        <v>0.002098982688039541</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01416186429560184</v>
+        <v>0.001268424093723297</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0162336565554142</v>
+        <v>2.404040424153209e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.008325414732098579</v>
+        <v>0.0003803077561315149</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.04462466761469841</v>
+        <v>0.000122321886010468</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.05590104311704636</v>
+        <v>2.494525688234717e-05</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.07171107083559036</v>
+        <v>0.002227112883701921</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.01588384807109833</v>
+        <v>0.0003352701896801591</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.04411051422357559</v>
+        <v>0.0005295053706504405</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.03672471642494202</v>
+        <v>0.0009604258229956031</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.07380019873380661</v>
+        <v>0.001440550666302443</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.02088038623332977</v>
+        <v>0.000190516046131961</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.02169599384069443</v>
+        <v>0.0004653736250475049</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.04077339172363281</v>
+        <v>0.0006318726809695363</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.03391838818788528</v>
+        <v>0.001084429328329861</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4529253542423248</v>
+        <v>0.004826509393751621</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0004655830562114716</v>
+        <v>0.0004913368029519916</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.05507683753967285</v>
+        <v>0.0009452679078094661</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.08109802007675171</v>
+        <v>0.003280420787632465</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.01517643500119448</v>
+        <v>0.0001649144251132384</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.003902183379977942</v>
+        <v>0.000544331269338727</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.06153940409421921</v>
+        <v>0.0002148093190044165</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.07766421884298325</v>
+        <v>0.0002070835034828633</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.05977848172187805</v>
+        <v>0.000102450605481863</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1178966462612152</v>
+        <v>0.001700947061181068</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1067434772849083</v>
+        <v>0.00157074979506433</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0001234859228134155</v>
+        <v>0.0003036768466699868</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1660318821668625</v>
+        <v>0.0001496829790994525</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1020474061369896</v>
+        <v>8.93850956344977e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.056782566010952</v>
+        <v>0.0007320184959098697</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.08850483596324921</v>
+        <v>0.001078207977116108</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02071904949843884</v>
+        <v>0.0008858020883053541</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.05740057677030563</v>
+        <v>0.0002258816530229524</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.06353694200515747</v>
+        <v>0.0005219365702942014</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.02632103860378265</v>
+        <v>0.0006422433070838451</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.07860123366117477</v>
+        <v>0.0006432906957343221</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.03461505100131035</v>
+        <v>0.0005151208024471998</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.04192406311631203</v>
+        <v>0.0002769459097180516</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.02526227571070194</v>
+        <v>0.0002550392528064549</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01764101162552834</v>
+        <v>0.0003335697401780635</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.04837235808372498</v>
+        <v>0.0004090604488737881</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.03169335424900055</v>
+        <v>0.0001084231334971264</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2325417250394821</v>
+        <v>0.003179855411872268</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0233695600181818</v>
+        <v>0.0001560297678224742</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.06303614377975464</v>
+        <v>0.001361277769319713</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.002233951818197966</v>
+        <v>0.0007262713043019176</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.1220659613609314</v>
+        <v>0.001035879133269191</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.04545758664608002</v>
+        <v>0.001136478851549327</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.002139764837920666</v>
+        <v>0.000187135228770785</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.07182016968727112</v>
+        <v>0.001363846939057112</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0433635301887989</v>
+        <v>0.0004662337596528232</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1081921830773354</v>
+        <v>0.002101585036143661</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.05011529847979546</v>
+        <v>0.0008645453490316868</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02215655148029327</v>
+        <v>0.001070996280759573</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.03623306751251221</v>
+        <v>7.843338244128972e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.04971250519156456</v>
+        <v>0.0002329342823941261</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.01834201253950596</v>
+        <v>4.179629468126222e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.006742009427398443</v>
+        <v>3.481714520603418e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.04397245496511459</v>
+        <v>0.0004308878851588815</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.04612366855144501</v>
+        <v>6.544694770127535e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0089256651699543</v>
+        <v>0.001192696276120842</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.04711798205971718</v>
+        <v>0.0003267621505074203</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1148508191108704</v>
+        <v>0.001497600227594376</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0807371661067009</v>
+        <v>0.001155279809609056</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.06893425434827805</v>
+        <v>0.0007656802772544324</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.05348671227693558</v>
+        <v>0.0001424277143087238</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.06495518237352371</v>
+        <v>0.0001634799409657717</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.02166041359305382</v>
+        <v>0.0009051562519744039</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.03497403487563133</v>
+        <v>0.0002672370756044984</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0893903374671936</v>
+        <v>0.002118865493685007</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.04821222648024559</v>
+        <v>0.0007067862898111343</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.05798253417015076</v>
+        <v>0.001231163623742759</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.03434175997972488</v>
+        <v>0.000460182927781716</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.05637377500534058</v>
+        <v>0.000244457449298352</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.02422190085053444</v>
+        <v>3.121713962173089e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.02099743857979774</v>
+        <v>6.540618778672069e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02949032187461853</v>
+        <v>0.0006930484087206423</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.04019360244274139</v>
+        <v>0.000129145773826167</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.08130438625812531</v>
+        <v>0.002734104637056589</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.008648927323520184</v>
+        <v>0.0004205456643830985</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1247633397579193</v>
+        <v>0.001490224152803421</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06534803658723831</v>
+        <v>0.0002569024218246341</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02559979259967804</v>
+        <v>0.004286759532988071</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.05907139182090759</v>
+        <v>0.0007389606907963753</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.002264704555273056</v>
+        <v>0.002147067571058869</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.005065028090029955</v>
+        <v>0.001282686251215637</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.07654804736375809</v>
+        <v>0.0002015065110754222</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.032911516726017</v>
+        <v>0.0006636350299231708</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.04613739252090454</v>
+        <v>0.0006337175145745277</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.01909743063151836</v>
+        <v>0.0004615727812051773</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0310723539441824</v>
+        <v>0.0004346040659584105</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09830369800329208</v>
+        <v>0.0006517167203128338</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.007081108167767525</v>
+        <v>0.0008136041578836739</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.01720951125025749</v>
+        <v>0.0006929828086867929</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.05534880608320236</v>
+        <v>0.002458051778376102</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.03668467327952385</v>
+        <v>8.883493137545884e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.001459415070712566</v>
+        <v>0.0005120396963320673</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.1192661300301552</v>
+        <v>0.0001721446315059438</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.02074672654271126</v>
+        <v>0.0006822258583270013</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.08246716111898422</v>
+        <v>0.0006967924418859184</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01055597700178623</v>
+        <v>0.001383039285428822</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.005771026946604252</v>
+        <v>0.0003660674556158483</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.03340308740735054</v>
+        <v>0.002258175984025002</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.02466641366481781</v>
+        <v>0.002003215253353119</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001034971326589584</v>
+        <v>0.0001710619399091229</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.05126943066716194</v>
+        <v>0.002119270619004965</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.006413434166461229</v>
+        <v>5.485440487973392e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.001392929814755917</v>
+        <v>0.0009823795408010483</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.005063612479716539</v>
+        <v>0.0003964247880503535</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.03551601618528366</v>
+        <v>0.0004785573401022702</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.02447226271033287</v>
+        <v>4.926499968860298e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.01561714522540569</v>
+        <v>0.0002806110423989594</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.01553083397448063</v>
+        <v>0.0005588937783613801</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.03468825668096542</v>
+        <v>0.0001555682101752609</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.07522207498550415</v>
+        <v>0.001500523998402059</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.004857000894844532</v>
+        <v>0.000183425669092685</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.06782400608062744</v>
+        <v>0.0008118411060422659</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.07745096832513809</v>
+        <v>0.0001419603504473343</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.192469134926796</v>
+        <v>0.00031613590545021</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.05139131098985672</v>
+        <v>0.0001395873841829598</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.07052847743034363</v>
+        <v>0.0005745443049818277</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.00670052133500576</v>
+        <v>0.001088659279048443</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.03125623241066933</v>
+        <v>0.0003046819183509797</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.08883625268936157</v>
+        <v>0.00235058506950736</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.02448924072086811</v>
+        <v>0.0007978006615303457</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.04004659503698349</v>
+        <v>0.001256665331311524</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.03613606467843056</v>
+        <v>0.0002118698321282864</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.05661088228225708</v>
+        <v>0.0004940894432365894</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.03559290617704391</v>
+        <v>0.0001629884354770184</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.009298268705606461</v>
+        <v>2.877978840842843e-05</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.04038657993078232</v>
+        <v>0.0007285280153155327</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.01518197357654572</v>
+        <v>0.0003936141147278249</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.05041535943746567</v>
+        <v>0.001038663787767291</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.03088845871388912</v>
+        <v>0.001360924448817968</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.05808612331748009</v>
+        <v>0.0004330287338234484</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.02329122461378574</v>
+        <v>0.000444505043560639</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.008379824459552765</v>
+        <v>0.0002969944034703076</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.002169754356145859</v>
+        <v>0.000270889897365123</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.05221888050436974</v>
+        <v>0.0007058614864945412</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.07078298926353455</v>
+        <v>0.001055923756211996</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.02867414243519306</v>
+        <v>0.0001686403556959704</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.01106442790478468</v>
+        <v>0.001178576378151774</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.005323079880326986</v>
+        <v>0.0006765661528334022</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.06364330649375916</v>
+        <v>0.0007184782298281789</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.1924760043621063</v>
+        <v>0.0004663607687689364</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.04143210127949715</v>
+        <v>0.0008617457933723927</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.01344587840139866</v>
+        <v>0.000503596558701247</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.004026294685900211</v>
+        <v>0.001076097250916064</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0463278517127037</v>
+        <v>0.001472532982006669</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.06768464297056198</v>
+        <v>0.001212194096297026</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.04107039049267769</v>
+        <v>0.001655536470934749</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.04535111412405968</v>
+        <v>8.360273204743862e-05</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.01710203848779202</v>
+        <v>0.0009149829857051373</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.1001198962330818</v>
+        <v>0.001629017642699182</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.05011771246790886</v>
+        <v>0.0004406388325151056</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.1947163343429565</v>
+        <v>0.0008515854133293033</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.01581853814423084</v>
+        <v>0.0009301126701757312</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.04654571041464806</v>
+        <v>0.0007304249447770417</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00184524292126298</v>
+        <v>0.002444052370265126</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00896625779569149</v>
+        <v>0.006768241990357637</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0005659818416461349</v>
+        <v>0.003555992618203163</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002728902967646718</v>
+        <v>4.341115709394217e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002551334444433451</v>
+        <v>0.000816320301964879</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001444214372895658</v>
+        <v>0.005065084435045719</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004533364262897521</v>
+        <v>0.001208057277835906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0007328447536565363</v>
+        <v>0.001805711886845529</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004747906932607293</v>
+        <v>0.003173429751768708</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00183688523247838</v>
+        <v>0.001161910244263709</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007365865167230368</v>
+        <v>0.01000275369733572</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008300119079649448</v>
+        <v>0.004151597153395414</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002420640317723155</v>
+        <v>0.003012676257640123</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002722430508583784</v>
+        <v>0.001383960363455117</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001859318581409752</v>
+        <v>0.003181527834385633</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001448256778530777</v>
+        <v>0.0006122916238382459</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002628772053867579</v>
+        <v>0.0009439949644729495</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0007069827406667173</v>
+        <v>0.003384294686838984</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004006645176559687</v>
+        <v>0.0002948562323581427</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001685163704678416</v>
+        <v>0.001552270958200097</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0004136772186029702</v>
+        <v>0.0003137820167466998</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001246458617970347</v>
+        <v>0.0002842828980647027</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0005144156748428941</v>
+        <v>0.001177386147901416</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001229327521286905</v>
+        <v>0.0003600894124247134</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.000170751620316878</v>
+        <v>0.001461980398744345</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000452018401119858</v>
+        <v>0.001203246181830764</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0007573282928206027</v>
+        <v>0.0006691874586977065</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0002073992509394884</v>
+        <v>0.001183398300781846</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0007711341604590416</v>
+        <v>0.0002259642205899581</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.001787145854905248</v>
+        <v>0.0008317952742800117</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001768899150192738</v>
+        <v>0.00112109596375376</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.189811731223017e-05</v>
+        <v>0.002355109667405486</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001211621565744281</v>
+        <v>0.001239278120920062</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001662665978074074</v>
+        <v>0.001067277742549777</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0002761766081675887</v>
+        <v>0.003087729215621948</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.001124974922277033</v>
+        <v>0.0008422959363088012</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001709240139462054</v>
+        <v>0.0004951052833348513</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001464559230953455</v>
+        <v>0.001763887237757444</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0002722425269894302</v>
+        <v>0.0003848483611363918</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.666839959099889e-05</v>
+        <v>0.00018711929442361</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0001548399159219116</v>
+        <v>0.0005416446947492659</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0006403458537533879</v>
+        <v>0.0002260956971440464</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0005911082844249904</v>
+        <v>0.0007430643308907747</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0005244360654614866</v>
+        <v>0.001706002047285438</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.000990769942291081</v>
+        <v>0.0002744746743701398</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0007570552406832576</v>
+        <v>0.0004973744507879019</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006599448621273041</v>
+        <v>0.008479714393615723</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0003570106346160173</v>
+        <v>0.00282796542160213</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0004923645756207407</v>
+        <v>0.001124307978898287</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001406378927640617</v>
+        <v>0.0008344000088982284</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001546453102491796</v>
+        <v>0.002254043007269502</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0007778802537359297</v>
+        <v>0.001282281707972288</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0005877536605112255</v>
+        <v>0.001671579666435719</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.671659993007779e-05</v>
+        <v>4.145190905546769e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0003288333537057042</v>
+        <v>0.0002193672698922455</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002154665067791939</v>
+        <v>0.002532681450247765</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0008105310844257474</v>
+        <v>0.0001041231444105506</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0001409237302141264</v>
+        <v>0.000348918663803488</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0031379668507725</v>
+        <v>0.0005299540353007615</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.000331607589032501</v>
+        <v>4.766702477354556e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0001951391896000132</v>
+        <v>0.0003787289606407285</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002016541315242648</v>
+        <v>0.000506935641169548</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0001346420176560059</v>
+        <v>0.002086380496621132</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001433126162737608</v>
+        <v>0.0001039622438838705</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001397645915858448</v>
+        <v>0.001179500366561115</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0007155826315283775</v>
+        <v>0.0004278539854567498</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.001287781866267323</v>
+        <v>0.0009688008576631546</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.00229240651242435</v>
+        <v>0.002424105070531368</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.059079659171402e-05</v>
+        <v>0.00124585663434118</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0005922982236370444</v>
+        <v>0.0007024969672784209</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0007426868542097509</v>
+        <v>8.532601350452751e-05</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0003913101390935481</v>
+        <v>0.0008842188399285078</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.000416350201703608</v>
+        <v>0.0001477713813073933</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003187096212059259</v>
+        <v>0.005827630404382944</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0007978384965099394</v>
+        <v>0.0006295721977949142</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0003538144810590893</v>
+        <v>0.0001301232259720564</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0003775790682993829</v>
+        <v>0.0001549312146380544</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001112868194468319</v>
+        <v>0.0007534620235674083</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0002779387577902526</v>
+        <v>0.0009306365391239524</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0005429416196420789</v>
+        <v>0.0001976955391000956</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0002696324372664094</v>
+        <v>0.0004783747717738152</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.800357080763206e-05</v>
+        <v>0.0008798746857792139</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001884016674011946</v>
+        <v>0.001608306309208274</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.000327249348629266</v>
+        <v>0.0001773060503182933</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0005585451726801693</v>
+        <v>0.001147589646279812</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0002447992446832359</v>
+        <v>2.724851947277784e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0001865148660726845</v>
+        <v>0.0008334516896866262</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0006545245414599776</v>
+        <v>1.4521210687235e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>6.48415953037329e-05</v>
+        <v>0.0005680514150299132</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0002022158732870594</v>
+        <v>9.12111354409717e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002222358947619796</v>
+        <v>0.0008162129670381546</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001918503199703991</v>
+        <v>0.0007059492636471987</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0004239307017996907</v>
+        <v>0.00162101979367435</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.002038862090557814</v>
+        <v>0.0005083978758193552</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.002489377977326512</v>
+        <v>0.0005169566138647497</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0008674563723616302</v>
+        <v>0.002564081456512213</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0008017143118195236</v>
+        <v>0.0005104916635900736</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0004484466044232249</v>
+        <v>0.0005514816148206592</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0004617533995769918</v>
+        <v>0.0003467844217084348</v>
       </c>
       <c r="CV9" t="n">
-        <v>6.784126162528992e-05</v>
+        <v>0.0002941238926723599</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001613217988051474</v>
+        <v>0.001466645626351237</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0003312113985884935</v>
+        <v>0.0004057240439578891</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0009411877254024148</v>
+        <v>0.001348558813333511</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0003143256180919707</v>
+        <v>0.0005762346554547548</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0003856563125737011</v>
+        <v>0.001120032975450158</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0008160956203937531</v>
+        <v>0.0004484004166442901</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0003203646920155734</v>
+        <v>0.0007438876200467348</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.000200435591978021</v>
+        <v>0.0001810232497518882</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0003815751988440752</v>
+        <v>0.001817582407966256</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.002122409641742706</v>
+        <v>0.001414016354829073</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0003890867810696363</v>
+        <v>0.0008741854107938707</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001512325135990977</v>
+        <v>0.002098948461934924</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002506603021174669</v>
+        <v>0.0006008322234265506</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0006808565813116729</v>
+        <v>0.005452712066471577</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002271532546728849</v>
+        <v>0.001192739699035883</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.00047032639849931</v>
+        <v>0.002147601917386055</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0009019030840136111</v>
+        <v>7.600616663694382e-05</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0004425676306709647</v>
+        <v>0.001046609482727945</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.001200926606543362</v>
+        <v>0.001039846916683018</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001006978331133723</v>
+        <v>0.001445150119252503</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0006992467679083347</v>
+        <v>0.0008755698800086975</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0003504329069983214</v>
+        <v>0.0002246350486529991</v>
       </c>
       <c r="DS9" t="n">
-        <v>2.330722782062367e-05</v>
+        <v>0.0003193180309608579</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001185171422548592</v>
+        <v>0.0004054657183587551</v>
       </c>
       <c r="DU9" t="n">
-        <v>3.039314469788224e-05</v>
+        <v>0.002062880666926503</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0006439801072701812</v>
+        <v>0.0007441519410349429</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001395202416460961</v>
+        <v>0.0003311852924525738</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0004348658549133688</v>
+        <v>9.0085686679231e-06</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0006104203639551997</v>
+        <v>0.001983406720682979</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0006441051955334842</v>
+        <v>5.7650962844491e-05</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0008960552513599396</v>
+        <v>0.002342786639928818</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.000296986021567136</v>
+        <v>0.0006469418294727802</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0001313509128522128</v>
+        <v>0.0001161790642072447</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001326639205217361</v>
+        <v>0.0002187106438213959</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0002312526776222512</v>
+        <v>0.002390979323536158</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0005740144988521934</v>
+        <v>0.001195554155856371</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0007871569250710309</v>
+        <v>0.0006045061163604259</v>
       </c>
       <c r="EH9" t="n">
-        <v>6.249453872442245e-05</v>
+        <v>0.001048185513354838</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001804179046303034</v>
+        <v>0.001931381644681096</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0002962687867693603</v>
+        <v>0.0002625298511702567</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0002935934462584555</v>
+        <v>0.00027116370620206</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0007370791863650084</v>
+        <v>0.0007292500813491642</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0002983923477586359</v>
+        <v>7.271792856045067e-05</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0003332191554363817</v>
+        <v>0.000890047405846417</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0009559960453771055</v>
+        <v>0.001202510320581496</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.000536539766471833</v>
+        <v>0.000798095716163516</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0004771348612848669</v>
+        <v>0.0005837946082465351</v>
       </c>
       <c r="ER9" t="n">
-        <v>3.865323378704488e-05</v>
+        <v>7.499218918383121e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0005227879155427217</v>
+        <v>0.0035509227309376</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0008134166710078716</v>
+        <v>0.003323558485135436</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0009866401087492704</v>
+        <v>0.00153419142588973</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.001306610298343003</v>
+        <v>0.0003160094493068755</v>
       </c>
       <c r="EW9" t="n">
-        <v>3.195536555722356e-05</v>
+        <v>0.0007681786082684994</v>
       </c>
       <c r="EX9" t="n">
-        <v>2.272634083055891e-05</v>
+        <v>0.0004807530203834176</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001411139615811408</v>
+        <v>0.001799549092538655</v>
       </c>
       <c r="EZ9" t="n">
-        <v>6.994975410634652e-05</v>
+        <v>0.0004661681596189737</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0004579143133014441</v>
+        <v>0.00116955628618598</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0002611886884551495</v>
+        <v>8.692208211869001e-06</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0004416737356223166</v>
+        <v>0.0006247045239433646</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0006745270802639425</v>
+        <v>0.0002297091268701479</v>
       </c>
       <c r="FE9" t="n">
-        <v>6.651593139395118e-05</v>
+        <v>0.000339882739353925</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0003975335275754333</v>
+        <v>0.0003632974403444678</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0008704114588908851</v>
+        <v>0.0005597638664767146</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001274081645533442</v>
+        <v>0.002326541813090444</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.001013317261822522</v>
+        <v>0.002537642838433385</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0005569786299020052</v>
+        <v>0.001747893868014216</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001916865003295243</v>
+        <v>0.001153762568719685</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0002280140615766868</v>
+        <v>0.001872615772299469</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0004976560012437403</v>
+        <v>0.0004417616873979568</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0002236366126453504</v>
+        <v>0.003237568773329258</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002762411895673722</v>
+        <v>0.002038394799456</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001664888812229037</v>
+        <v>0.001099439337849617</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0008814519387669861</v>
+        <v>0.0005527123576030135</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0009028523927554488</v>
+        <v>0.0005865172715857625</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0004494255699682981</v>
+        <v>0.002692765789106488</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.003052204847335815</v>
+        <v>0.0002145930775441229</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0008236292633228004</v>
+        <v>0.001269680680707097</v>
       </c>
       <c r="FV9" t="n">
-        <v>3.927297075279057e-05</v>
+        <v>0.0006545621436089277</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0003424606402404606</v>
+        <v>0.003100875066593289</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0006175702437758446</v>
+        <v>0.0009752298356033862</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0007463368237949908</v>
+        <v>0.002343549858778715</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.001286855898797512</v>
+        <v>9.133058483712375e-06</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0007013785070739686</v>
+        <v>0.002083486644551158</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.001408546813763678</v>
+        <v>0.0007298238924704492</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0003777831443585455</v>
+        <v>0.001583646750077605</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001225161366164684</v>
+        <v>0.001221463433466852</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.001543051563203335</v>
+        <v>0.0002604617038741708</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.001496665878221393</v>
+        <v>0.001470391056500375</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0006322582485154271</v>
+        <v>0.001587063074111938</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0004794306587427855</v>
+        <v>0.005211235024034977</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01330834068357944</v>
+        <v>0.02482210285961628</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001411022618412971</v>
+        <v>0.006590601988136768</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006576741114258766</v>
+        <v>0.0134076252579689</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002220646245405078</v>
+        <v>0.006924441549926996</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001428994466550648</v>
+        <v>0.003324799006804824</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0009758439846336842</v>
+        <v>0.01064541842788458</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001020357245579362</v>
+        <v>0.006153942551463842</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001007577870041132</v>
+        <v>0.005489836446940899</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001532677910290658</v>
+        <v>0.008113582618534565</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009643423371016979</v>
+        <v>0.02561882883310318</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001639450347283855</v>
+        <v>0.008330637589097023</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006182386539876461</v>
+        <v>0.01971657387912273</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003874585963785648</v>
+        <v>0.009497864171862602</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002672539791092277</v>
+        <v>0.003195891156792641</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0007666717283427715</v>
+        <v>0.01127690821886063</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001287612598389387</v>
+        <v>0.003165693720802665</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0002365937689319253</v>
+        <v>0.006146837491542101</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005487995804287493</v>
+        <v>0.002110872883349657</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001994959078729153</v>
+        <v>0.002674044575542212</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0001204137151944451</v>
+        <v>0.000272992008831352</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0008402570383623242</v>
+        <v>0.0006604756345041096</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003933372208848596</v>
+        <v>0.0003703792172018439</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001261455588974059</v>
+        <v>0.003545149927958846</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001359288347885013</v>
+        <v>0.002771285129711032</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0007549145957455039</v>
+        <v>0.00693088723346591</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0003828477347269654</v>
+        <v>0.005948420148342848</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00163357425481081</v>
+        <v>0.006471154280006886</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002027652226388454</v>
+        <v>9.102886542677879e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0008800950017757714</v>
+        <v>0.006048610433936119</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001844479411374778</v>
+        <v>0.0001263367012143135</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0002682373160496354</v>
+        <v>0.008951793424785137</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0004851327685173601</v>
+        <v>0.003651089267805219</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0005882203113287687</v>
+        <v>0.002413742709904909</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0003166587557643652</v>
+        <v>0.001605934579856694</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002693950664252043</v>
+        <v>0.001261053141206503</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001097478670999408</v>
+        <v>0.002758177230134606</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.001332619809545577</v>
+        <v>0.01007187180221081</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0004131060559302568</v>
+        <v>0.001316212583333254</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0005254875868558884</v>
+        <v>0.002848273608833551</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.001296440022997558</v>
+        <v>0.004352851305156946</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001342775532975793</v>
+        <v>0.005116080865263939</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0005842496175318956</v>
+        <v>0.002160632982850075</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0007508108392357826</v>
+        <v>0.0004858018073718995</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0002209385274909437</v>
+        <v>0.003174485405907035</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0009498700965195894</v>
+        <v>0.006185775157064199</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01022919081151485</v>
+        <v>0.01904254779219627</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0003070685197599232</v>
+        <v>0.00179259164724499</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.001551054883748293</v>
+        <v>0.0045504798181355</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0007096054032444954</v>
+        <v>0.01470024790614843</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0003247779968660325</v>
+        <v>0.003075774991884828</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0005130760837346315</v>
+        <v>0.001604435499757528</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0001983540860237554</v>
+        <v>0.001366042764857411</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0004445673548616469</v>
+        <v>0.0012956946156919</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0007884851656854153</v>
+        <v>0.004269786179065704</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.003064665710553527</v>
+        <v>0.005720102228224277</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.002626841655001044</v>
+        <v>0.002450160449370742</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0007888429099693894</v>
+        <v>0.002959860488772392</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.002972551388666034</v>
+        <v>0.001365408301353455</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001925182295963168</v>
+        <v>0.001422944595105946</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.001457614125683904</v>
+        <v>0.003401762340217829</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0008766507962718606</v>
+        <v>0.004133249633014202</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.584170968271792e-05</v>
+        <v>0.004071597475558519</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.002233346924185753</v>
+        <v>0.00112831115256995</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.002607941161841154</v>
+        <v>0.004638895392417908</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001248219981789589</v>
+        <v>0.0004041618667542934</v>
       </c>
       <c r="BO10" t="n">
-        <v>9.550330287311226e-05</v>
+        <v>0.004303311463445425</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.002234750427305698</v>
+        <v>0.0002475996734574437</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001015006680972874</v>
+        <v>0.0009197628824040294</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0003300649987068027</v>
+        <v>0.002536435378715396</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0006578397005796432</v>
+        <v>0.001847680425271392</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0003753188066184521</v>
+        <v>0.0007374160340987146</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0008688199450261891</v>
+        <v>0.0005438752705231309</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.005005756393074989</v>
+        <v>0.01282831374555826</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001234850496985018</v>
+        <v>0.0009164528455585241</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0009650713764131069</v>
+        <v>0.01013878732919693</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0003319256647955626</v>
+        <v>0.002302050124853849</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002251037629321218</v>
+        <v>0.003872115863487124</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0005155704566277564</v>
+        <v>0.002809567144140601</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0006170074921101332</v>
+        <v>0.0008920744294300675</v>
       </c>
       <c r="CC10" t="n">
-        <v>8.91252129804343e-05</v>
+        <v>0.005164854228496552</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0005033980123698711</v>
+        <v>0.002556972205638885</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.002181990072131157</v>
+        <v>0.007532504387199879</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0006299341330304742</v>
+        <v>0.00141728762537241</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0005236188299022615</v>
+        <v>0.005651487037539482</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0003934308770112693</v>
+        <v>0.0004215963126625866</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0005218638107180595</v>
+        <v>0.0003115090657956898</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0004099975049030036</v>
+        <v>0.0004606923903338611</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001356721331831068</v>
+        <v>6.607233081012964e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0002401773963356391</v>
+        <v>0.001937419874593616</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.002587442751973867</v>
+        <v>0.003415593877434731</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.002124069025740027</v>
+        <v>0.005335276015102863</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0003525232605170459</v>
+        <v>6.734789349138737e-05</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.00272090919315815</v>
+        <v>0.005717366002500057</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.002277882071211934</v>
+        <v>0.002626751083880663</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001114569487981498</v>
+        <v>0.00220001838169992</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.001010827720165253</v>
+        <v>0.001513543771579862</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.002379766199737787</v>
+        <v>0.00024615996517241</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0001550749293528497</v>
+        <v>0.003334851935505867</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0004408214008435607</v>
+        <v>0.002144401660189033</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.001752830110490322</v>
+        <v>0.007543631829321384</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0008242731564678252</v>
+        <v>0.001156467013061047</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001113079721108079</v>
+        <v>0.006175160873681307</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0004609037423506379</v>
+        <v>0.001379450201056898</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0004572851466946304</v>
+        <v>0.0006455830298364162</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0003176434547640383</v>
+        <v>0.0005866523133590817</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001697397674433887</v>
+        <v>0.0004094322212040424</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0001418769534211606</v>
+        <v>0.002377786673605442</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001221846439875662</v>
+        <v>0.0002323650987818837</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.001133616780862212</v>
+        <v>0.01316679734736681</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001008065533824265</v>
+        <v>0.001411102246493101</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.002697514602914453</v>
+        <v>0.008394619449973106</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0003551484260242432</v>
+        <v>0.001549293636344373</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0003855769464280456</v>
+        <v>0.01540923025459051</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0009185680537484586</v>
+        <v>0.005220794584602118</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0005944286822341383</v>
+        <v>0.0110584981739521</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0004985821433365345</v>
+        <v>0.005497016943991184</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0009217955521307886</v>
+        <v>0.002573243342339993</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.000450220366474241</v>
+        <v>0.0009939956944435835</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001172541291452944</v>
+        <v>8.430657908320427e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0006583422655239701</v>
+        <v>0.001831328961998224</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0007182300905697048</v>
+        <v>0.0007727394113317132</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.001098769949749112</v>
+        <v>0.002472397405654192</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0004904726520180702</v>
+        <v>0.002994576003402472</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0003139304171781987</v>
+        <v>0.004781210795044899</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0002798899658955634</v>
+        <v>0.01205676794052124</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0001759914885042235</v>
+        <v>0.0005572652444243431</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0005177300772629678</v>
+        <v>0.002808280754834414</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0006556288572028279</v>
+        <v>0.00101104227360338</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.000567612936720252</v>
+        <v>0.005131259560585022</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001723900088109076</v>
+        <v>0.0009753454942256212</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0007380580063909292</v>
+        <v>0.007410187274217606</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0002784720854833722</v>
+        <v>0.001503291656263173</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0002798294590320438</v>
+        <v>0.008367357775568962</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0001032974032568745</v>
+        <v>0.008279937319457531</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0003613283624872565</v>
+        <v>0.0001116365310736001</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001672253827564418</v>
+        <v>0.007988809607923031</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.000178715301444754</v>
+        <v>0.0009773510973900557</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.001282047713175416</v>
+        <v>0.003634986001998186</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0007013644208200276</v>
+        <v>0.000935824413318187</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.000432588771218434</v>
+        <v>0.002602027030661702</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0004551797755993903</v>
+        <v>0.0009174814913421869</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0002710317494347692</v>
+        <v>0.001788200112059712</v>
       </c>
       <c r="EN10" t="n">
-        <v>8.419639198109508e-05</v>
+        <v>0.001891851308755577</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0008465524297207594</v>
+        <v>0.002461370779201388</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.001169335446320474</v>
+        <v>0.006081176921725273</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0005399510264396667</v>
+        <v>0.002787238918244839</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.001104254624806345</v>
+        <v>0.006634286139160395</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0002220741007477045</v>
+        <v>0.0004704900493379682</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.002188240177929401</v>
+        <v>0.0003807996399700642</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0008468362502753735</v>
+        <v>0.0002869179006665945</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0009528417722322047</v>
+        <v>0.003642424242570996</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0003598550392780453</v>
+        <v>0.004917690064758062</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.000125919163110666</v>
+        <v>0.001812899019569159</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.001761242398060858</v>
+        <v>0.008521757088601589</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0003826872853096575</v>
+        <v>0.001474256161600351</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0007515551405958831</v>
+        <v>0.006406029686331749</v>
       </c>
       <c r="FB10" t="n">
-        <v>7.661150448257104e-05</v>
+        <v>1.029636769089848e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.000728511658962816</v>
+        <v>0.001022702897898853</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0004845960938837379</v>
+        <v>0.001135582802817225</v>
       </c>
       <c r="FE10" t="n">
-        <v>5.951635102974251e-05</v>
+        <v>0.0003931528481189162</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0002424429985694587</v>
+        <v>0.002709755906835198</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0003762630512937903</v>
+        <v>0.00121539318934083</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0004190770850982517</v>
+        <v>0.003409188473597169</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0002248381933895871</v>
+        <v>0.006122356280684471</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.00144591520074755</v>
+        <v>0.0005037413793615997</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.001242225407622755</v>
+        <v>0.001923523843288422</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0008149106870405376</v>
+        <v>0.002214697422459722</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0005075590452179313</v>
+        <v>0.001821401063352823</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0002582828747108579</v>
+        <v>0.001445612637326121</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0007075658650137484</v>
+        <v>0.006054297089576721</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0008093536598607898</v>
+        <v>0.001175574027001858</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0008364191162399948</v>
+        <v>0.007244353648275137</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0001293075329158455</v>
+        <v>0.00220683915540576</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.001144153182394803</v>
+        <v>0.004920659586787224</v>
       </c>
       <c r="FT10" t="n">
-        <v>6.159502663649619e-05</v>
+        <v>0.003423209302127361</v>
       </c>
       <c r="FU10" t="n">
-        <v>7.2130515036406e-06</v>
+        <v>0.005600464530289173</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0003876295813824981</v>
+        <v>7.991131860762835e-05</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0003472212702035904</v>
+        <v>0.006601784378290176</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0006314755883067846</v>
+        <v>0.003942008130252361</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001870795036666095</v>
+        <v>0.006987691391259432</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0006138602620922029</v>
+        <v>0.004348536022007465</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0006985203945077956</v>
+        <v>0.0006680574733763933</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0002004161797231063</v>
+        <v>0.005850105546414852</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0003485313500277698</v>
+        <v>0.006947112735360861</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.001737688900902867</v>
+        <v>0.002255865372717381</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.002078122459352016</v>
+        <v>0.001748041016981006</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0003558298049028963</v>
+        <v>0.007265860680490732</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.000427215825766325</v>
+        <v>0.003336653579026461</v>
       </c>
     </row>
     <row r="11">
@@ -6689,1709 +6689,1709 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.119409536760486e-09</v>
+        <v>2.450967206968357e-10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.206363720029913e-08</v>
+        <v>1.59922586284722e-09</v>
       </c>
       <c r="C12" t="n">
-        <v>1.67946168083688e-09</v>
+        <v>2.08644768129318e-11</v>
       </c>
       <c r="D12" t="n">
-        <v>2.459874792748451e-08</v>
+        <v>3.362135014839396e-10</v>
       </c>
       <c r="E12" t="n">
-        <v>3.385614677497983e-09</v>
+        <v>5.882733744577706e-10</v>
       </c>
       <c r="F12" t="n">
-        <v>3.417871541344653e-09</v>
+        <v>1.196268750724983e-09</v>
       </c>
       <c r="G12" t="n">
-        <v>1.42471345832007e-09</v>
+        <v>6.511413075394046e-10</v>
       </c>
       <c r="H12" t="n">
-        <v>6.039340139096794e-10</v>
+        <v>7.859791151254569e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>1.017763651134374e-09</v>
+        <v>2.262051934653897e-10</v>
       </c>
       <c r="J12" t="n">
-        <v>4.960450716851028e-09</v>
+        <v>1.531879900706912e-10</v>
       </c>
       <c r="K12" t="n">
-        <v>6.475616487477964e-09</v>
+        <v>2.165002843668162e-09</v>
       </c>
       <c r="L12" t="n">
-        <v>4.269350428742769e-10</v>
+        <v>4.135697062590538e-10</v>
       </c>
       <c r="M12" t="n">
-        <v>1.373858360409486e-08</v>
+        <v>9.891233387904208e-10</v>
       </c>
       <c r="N12" t="n">
-        <v>6.469265567687899e-09</v>
+        <v>1.432996943329101e-09</v>
       </c>
       <c r="O12" t="n">
-        <v>2.933905562940708e-09</v>
+        <v>1.662981641281647e-09</v>
       </c>
       <c r="P12" t="n">
-        <v>4.059522495936108e-09</v>
+        <v>3.906559520316932e-10</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.834911220858885e-09</v>
+        <v>1.675671268408507e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>2.052936709517894e-10</v>
+        <v>8.757447544915919e-10</v>
       </c>
       <c r="S12" t="n">
-        <v>1.517477699053416e-09</v>
+        <v>8.606004797684363e-11</v>
       </c>
       <c r="T12" t="n">
-        <v>2.401961962661403e-09</v>
+        <v>8.634178094713008e-11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.573864816251103e-09</v>
+        <v>2.934253118258567e-10</v>
       </c>
       <c r="V12" t="n">
-        <v>8.938446094397534e-10</v>
+        <v>2.840770396694836e-10</v>
       </c>
       <c r="W12" t="n">
-        <v>3.920464397566548e-09</v>
+        <v>4.000552389360479e-10</v>
       </c>
       <c r="X12" t="n">
-        <v>1.765560364574981e-09</v>
+        <v>4.03426153594566e-10</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.033221199355012e-09</v>
+        <v>3.357264743986121e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.629335555364264e-12</v>
+        <v>1.360695722762983e-10</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.393893749896847e-09</v>
+        <v>1.36933089867064e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.250530790031235e-10</v>
+        <v>2.238742802251892e-10</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.5997209112939e-09</v>
+        <v>4.558267652221559e-10</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.054725862204009e-09</v>
+        <v>1.627823986716237e-10</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.242826895899498e-09</v>
+        <v>3.8245193123565e-10</v>
       </c>
       <c r="AF12" t="n">
-        <v>4.978605971928118e-09</v>
+        <v>1.01526531626206e-09</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.977507129742207e-09</v>
+        <v>1.199633281601109e-09</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.595074294868937e-09</v>
+        <v>1.954421000038842e-11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.51120793656645e-09</v>
+        <v>1.31962141214359e-09</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.746661149049089e-10</v>
+        <v>9.522876237566535e-11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.863141418922964e-09</v>
+        <v>1.924419998355908e-11</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.28595609108595e-09</v>
+        <v>3.475806586994423e-10</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.566324014934395e-10</v>
+        <v>4.831833821938858e-10</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.741780719655139e-09</v>
+        <v>1.428179102758165e-10</v>
       </c>
       <c r="AO12" t="n">
-        <v>8.532300976860085e-10</v>
+        <v>3.882671684163341e-10</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.100058793530479e-09</v>
+        <v>4.888391913482337e-10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.893461914510453e-09</v>
+        <v>2.497075879404065e-10</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.890538392501639e-09</v>
+        <v>3.267450754407264e-10</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.67617497659478e-09</v>
+        <v>1.035849878094908e-11</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.50235445884573e-11</v>
+        <v>1.767001961416881e-10</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.165338906072293e-09</v>
+        <v>2.050763781014098e-09</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.327787153790013e-11</v>
+        <v>6.271843600025306e-10</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.152447737240436e-08</v>
+        <v>2.204880722445068e-10</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.144827870864674e-09</v>
+        <v>1.275772487652205e-09</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.51027557127037e-09</v>
+        <v>1.386790349222622e-09</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.214332412402541e-09</v>
+        <v>6.543641323242255e-11</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.027887718332067e-09</v>
+        <v>1.819684680715028e-10</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.082978843911178e-09</v>
+        <v>2.63964766711311e-10</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.674549470782495e-11</v>
+        <v>3.028177153474587e-10</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.503611679609662e-10</v>
+        <v>5.579518791432037e-11</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.385820569410612e-09</v>
+        <v>4.271675790867846e-10</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.114813213438538e-09</v>
+        <v>8.341141666257101e-11</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.963191996803062e-09</v>
+        <v>9.123449773440484e-10</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.684111460344752e-09</v>
+        <v>1.664881565943688e-10</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.495162603783797e-09</v>
+        <v>4.613157078559027e-12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.327826428455865e-09</v>
+        <v>9.706533354858493e-10</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.93664245435366e-10</v>
+        <v>3.730273867574851e-10</v>
       </c>
       <c r="BL12" t="n">
-        <v>5.068295227950159e-10</v>
+        <v>4.519882385034535e-11</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.117487657964489e-09</v>
+        <v>9.554480540074906e-10</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.749890759545792e-09</v>
+        <v>1.245786807047011e-10</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.536677007862863e-09</v>
+        <v>4.213986104506517e-11</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.639930413688262e-09</v>
+        <v>9.382030707882905e-10</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.08452299865769e-09</v>
+        <v>4.06970457333955e-10</v>
       </c>
       <c r="BR12" t="n">
-        <v>1.784195347021011e-09</v>
+        <v>6.673487318309412e-10</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.158345972589018e-10</v>
+        <v>4.959240795798792e-10</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.692529449925928e-10</v>
+        <v>1.582403513777919e-10</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.031145027840523e-10</v>
+        <v>3.834906697752771e-11</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.938144033099888e-09</v>
+        <v>1.217809852960272e-09</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.808756144860979e-09</v>
+        <v>2.525554487764481e-10</v>
       </c>
       <c r="BX12" t="n">
-        <v>5.064231700657729e-09</v>
+        <v>3.020833028166692e-10</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.951363680698705e-09</v>
+        <v>3.337944920467351e-10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>9.99709870441734e-10</v>
+        <v>8.82536932422795e-10</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.352111699328475e-09</v>
+        <v>4.981307588636241e-10</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.074904692506152e-09</v>
+        <v>3.507449886086533e-10</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.941284549251577e-09</v>
+        <v>3.399041881291254e-10</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.726071035574762e-10</v>
+        <v>1.437149878269484e-11</v>
       </c>
       <c r="CE12" t="n">
-        <v>2.272037447070829e-09</v>
+        <v>5.883726839073233e-10</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.305258428592083e-09</v>
+        <v>9.476874840430582e-11</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.416954858475151e-09</v>
+        <v>8.94152252239877e-11</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.01852315470552e-09</v>
+        <v>3.518442204253347e-10</v>
       </c>
       <c r="CI12" t="n">
-        <v>3.249467916965898e-10</v>
+        <v>3.995100084086545e-10</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.72464398318084e-09</v>
+        <v>4.438341708046245e-11</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.094792367872799e-09</v>
+        <v>2.896890019532528e-11</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.055791092914205e-09</v>
+        <v>9.667634748300458e-12</v>
       </c>
       <c r="CM12" t="n">
-        <v>4.020038524288339e-09</v>
+        <v>7.968579129880027e-10</v>
       </c>
       <c r="CN12" t="n">
-        <v>3.534939452265462e-09</v>
+        <v>1.122273829423648e-09</v>
       </c>
       <c r="CO12" t="n">
-        <v>2.748273553176972e-10</v>
+        <v>1.071630673088464e-09</v>
       </c>
       <c r="CP12" t="n">
-        <v>4.617239035553666e-09</v>
+        <v>4.808468623274109e-10</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.989651332579001e-09</v>
+        <v>3.63090169042124e-10</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.577731723045872e-09</v>
+        <v>7.253121991901423e-10</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.489759953760995e-09</v>
+        <v>4.419895283103159e-10</v>
       </c>
       <c r="CT12" t="n">
-        <v>8.408672869109068e-09</v>
+        <v>6.512795858171216e-11</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.854505771170523e-09</v>
+        <v>6.715739075957572e-12</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.800587539653066e-11</v>
+        <v>8.670503898189352e-11</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.225341910744305e-09</v>
+        <v>5.22005605407827e-10</v>
       </c>
       <c r="CX12" t="n">
-        <v>2.004988841619593e-09</v>
+        <v>3.160020162207289e-11</v>
       </c>
       <c r="CY12" t="n">
-        <v>4.16403933556353e-09</v>
+        <v>2.43043474235094e-10</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.35802835643517e-09</v>
+        <v>3.933168790659636e-10</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.712712471846345e-10</v>
+        <v>3.852110852520241e-10</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.378143155150724e-09</v>
+        <v>5.430332919442726e-11</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.279841455037456e-09</v>
+        <v>6.568216456837028e-12</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.596789811486587e-09</v>
+        <v>3.403179474337215e-11</v>
       </c>
       <c r="DE12" t="n">
-        <v>3.504780909935334e-09</v>
+        <v>2.144317640118132e-10</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.765964707800549e-09</v>
+        <v>3.836894690856241e-11</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.977160822898895e-09</v>
+        <v>4.104666884163777e-10</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.704624530418641e-08</v>
+        <v>2.055079162399664e-10</v>
       </c>
       <c r="DI12" t="n">
-        <v>6.64620225521162e-09</v>
+        <v>5.776212841368533e-11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>4.499445260819357e-11</v>
+        <v>6.911577976609351e-10</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.873982912239171e-09</v>
+        <v>1.080540171227717e-10</v>
       </c>
       <c r="DL12" t="n">
-        <v>1.028894480725739e-08</v>
+        <v>8.761122383127429e-10</v>
       </c>
       <c r="DM12" t="n">
-        <v>1.072741229179996e-09</v>
+        <v>6.003137986709817e-10</v>
       </c>
       <c r="DN12" t="n">
-        <v>6.025677179444244e-10</v>
+        <v>3.798936443200063e-10</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.286680428869147e-09</v>
+        <v>3.958155747607606e-10</v>
       </c>
       <c r="DP12" t="n">
-        <v>4.762241712086279e-09</v>
+        <v>1.613296995994773e-10</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.350970751407999e-09</v>
+        <v>1.81511000674206e-10</v>
       </c>
       <c r="DR12" t="n">
-        <v>2.866253678845965e-09</v>
+        <v>5.542714204276322e-11</v>
       </c>
       <c r="DS12" t="n">
-        <v>2.72648348342841e-09</v>
+        <v>3.75805331298551e-10</v>
       </c>
       <c r="DT12" t="n">
-        <v>9.403351430847806e-10</v>
+        <v>2.245520713817228e-10</v>
       </c>
       <c r="DU12" t="n">
-        <v>3.221201638758941e-10</v>
+        <v>2.126706727390015e-10</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.060389358073735e-09</v>
+        <v>1.59670471289175e-11</v>
       </c>
       <c r="DW12" t="n">
-        <v>5.74737368808087e-10</v>
+        <v>1.041228700482399e-10</v>
       </c>
       <c r="DX12" t="n">
-        <v>3.821080341026573e-09</v>
+        <v>3.385497437946583e-10</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.482965832939499e-09</v>
+        <v>4.16686574133962e-10</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.541619387701587e-09</v>
+        <v>9.136773976292645e-11</v>
       </c>
       <c r="EA12" t="n">
-        <v>4.59631799287763e-09</v>
+        <v>8.688692543223908e-10</v>
       </c>
       <c r="EB12" t="n">
-        <v>3.887092425713945e-09</v>
+        <v>5.406150527242914e-11</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.11388254123257e-10</v>
+        <v>2.554645106567222e-10</v>
       </c>
       <c r="ED12" t="n">
-        <v>1.952770833923978e-09</v>
+        <v>6.136736119266573e-10</v>
       </c>
       <c r="EE12" t="n">
-        <v>7.307550120572159e-10</v>
+        <v>9.737206596582837e-10</v>
       </c>
       <c r="EF12" t="n">
-        <v>5.678260084351905e-10</v>
+        <v>4.89887158616753e-11</v>
       </c>
       <c r="EG12" t="n">
-        <v>7.106702448744784e-10</v>
+        <v>1.838331153969364e-10</v>
       </c>
       <c r="EH12" t="n">
-        <v>1.363652191166409e-09</v>
+        <v>4.117425844718525e-10</v>
       </c>
       <c r="EI12" t="n">
-        <v>3.208353138717257e-09</v>
+        <v>2.719619529578665e-10</v>
       </c>
       <c r="EJ12" t="n">
-        <v>2.419733302616578e-09</v>
+        <v>1.888054435017494e-10</v>
       </c>
       <c r="EK12" t="n">
-        <v>2.96576624370104e-10</v>
+        <v>4.119251051371009e-10</v>
       </c>
       <c r="EL12" t="n">
-        <v>2.362471995809301e-09</v>
+        <v>8.195233380803302e-11</v>
       </c>
       <c r="EM12" t="n">
-        <v>9.809483225708959e-10</v>
+        <v>6.359656551380155e-11</v>
       </c>
       <c r="EN12" t="n">
-        <v>1.025528995057812e-09</v>
+        <v>5.083428677998825e-10</v>
       </c>
       <c r="EO12" t="n">
-        <v>5.708130634829445e-10</v>
+        <v>3.266849291083673e-11</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.165664231805863e-10</v>
+        <v>4.507603734715815e-10</v>
       </c>
       <c r="EQ12" t="n">
-        <v>2.236814511391572e-09</v>
+        <v>8.14134870630312e-11</v>
       </c>
       <c r="ER12" t="n">
-        <v>1.653171377569151e-09</v>
+        <v>5.588932788791467e-11</v>
       </c>
       <c r="ES12" t="n">
-        <v>7.433524018551907e-09</v>
+        <v>3.245349544656051e-10</v>
       </c>
       <c r="ET12" t="n">
-        <v>2.472302085276823e-10</v>
+        <v>3.511509971687587e-10</v>
       </c>
       <c r="EU12" t="n">
-        <v>1.154314199780515e-09</v>
+        <v>1.725692852505567e-11</v>
       </c>
       <c r="EV12" t="n">
-        <v>3.917727475766242e-09</v>
+        <v>2.606057036835807e-10</v>
       </c>
       <c r="EW12" t="n">
-        <v>7.756942865810856e-10</v>
+        <v>4.223345007048351e-10</v>
       </c>
       <c r="EX12" t="n">
-        <v>8.785957517076781e-10</v>
+        <v>3.627944819561968e-11</v>
       </c>
       <c r="EY12" t="n">
-        <v>2.215761130131e-09</v>
+        <v>6.373473970811006e-10</v>
       </c>
       <c r="EZ12" t="n">
-        <v>2.189790127005153e-09</v>
+        <v>5.868633357053454e-11</v>
       </c>
       <c r="FA12" t="n">
-        <v>3.673371606893738e-09</v>
+        <v>2.094301398969378e-10</v>
       </c>
       <c r="FB12" t="n">
-        <v>5.636249245100089e-10</v>
+        <v>1.885600980910951e-10</v>
       </c>
       <c r="FC12" t="n">
-        <v>7.840630228406198e-11</v>
+        <v>3.787024305257347e-10</v>
       </c>
       <c r="FD12" t="n">
-        <v>1.673463922990948e-09</v>
+        <v>1.427963580713509e-10</v>
       </c>
       <c r="FE12" t="n">
-        <v>1.442801322859566e-09</v>
+        <v>6.485753600848909e-11</v>
       </c>
       <c r="FF12" t="n">
-        <v>2.240163832212261e-09</v>
+        <v>2.205223365026043e-10</v>
       </c>
       <c r="FG12" t="n">
-        <v>1.935473170622259e-10</v>
+        <v>2.441666036023804e-10</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.685516060057068e-09</v>
+        <v>1.884847972144499e-10</v>
       </c>
       <c r="FI12" t="n">
-        <v>4.265413355852843e-09</v>
+        <v>4.445947499043257e-10</v>
       </c>
       <c r="FJ12" t="n">
-        <v>6.970416688290015e-09</v>
+        <v>4.322087410191244e-10</v>
       </c>
       <c r="FK12" t="n">
-        <v>1.929681303636244e-09</v>
+        <v>5.543109027339455e-11</v>
       </c>
       <c r="FL12" t="n">
-        <v>5.920053891550481e-10</v>
+        <v>1.941308225283933e-11</v>
       </c>
       <c r="FM12" t="n">
-        <v>3.37801187022535e-09</v>
+        <v>1.690689116484734e-10</v>
       </c>
       <c r="FN12" t="n">
-        <v>1.338949062734685e-09</v>
+        <v>1.59010610234489e-10</v>
       </c>
       <c r="FO12" t="n">
-        <v>1.109611069693983e-09</v>
+        <v>1.340378474878889e-09</v>
       </c>
       <c r="FP12" t="n">
-        <v>4.060791702897859e-09</v>
+        <v>4.778243911651714e-10</v>
       </c>
       <c r="FQ12" t="n">
-        <v>9.981672155490173e-10</v>
+        <v>2.909808782813883e-10</v>
       </c>
       <c r="FR12" t="n">
-        <v>8.059337086585572e-10</v>
+        <v>9.370004772080165e-10</v>
       </c>
       <c r="FS12" t="n">
-        <v>2.574446211767167e-10</v>
+        <v>2.376839836060185e-10</v>
       </c>
       <c r="FT12" t="n">
-        <v>5.671068947776803e-09</v>
+        <v>5.879520481588685e-11</v>
       </c>
       <c r="FU12" t="n">
-        <v>1.016449813207032e-09</v>
+        <v>4.027417843666115e-10</v>
       </c>
       <c r="FV12" t="n">
-        <v>1.567421525905388e-09</v>
+        <v>3.128594328050127e-10</v>
       </c>
       <c r="FW12" t="n">
-        <v>2.950756083919259e-09</v>
+        <v>1.053039544451906e-09</v>
       </c>
       <c r="FX12" t="n">
-        <v>9.908106557432461e-10</v>
+        <v>2.860246761660079e-10</v>
       </c>
       <c r="FY12" t="n">
-        <v>3.964749861751216e-09</v>
+        <v>2.421857714374198e-10</v>
       </c>
       <c r="FZ12" t="n">
-        <v>7.742759211559758e-10</v>
+        <v>2.699840906394968e-10</v>
       </c>
       <c r="GA12" t="n">
-        <v>4.308869927527326e-10</v>
+        <v>2.9828223224726e-10</v>
       </c>
       <c r="GB12" t="n">
-        <v>9.21452247837351e-10</v>
+        <v>2.521898800900146e-10</v>
       </c>
       <c r="GC12" t="n">
-        <v>2.98811708709934e-09</v>
+        <v>5.60259116877404e-10</v>
       </c>
       <c r="GD12" t="n">
-        <v>4.564142674912119e-10</v>
+        <v>1.101351565502284e-09</v>
       </c>
       <c r="GE12" t="n">
-        <v>8.777043092322856e-09</v>
+        <v>6.010654196586529e-10</v>
       </c>
       <c r="GF12" t="n">
-        <v>4.3309017483395e-10</v>
+        <v>1.582275699352209e-10</v>
       </c>
       <c r="GG12" t="n">
-        <v>3.510968848985385e-09</v>
+        <v>4.182526547324983e-10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.001026009442284703</v>
+        <v>0.0001503699168097228</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006094458978623152</v>
+        <v>0.0004003992362413555</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002809820289257914</v>
+        <v>8.611133671365678e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003596931230276823</v>
+        <v>3.655019827419892e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0007960060611367226</v>
+        <v>0.0002804819960147142</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00399483647197485</v>
+        <v>0.0005382609670050442</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003208111738786101</v>
+        <v>0.0003103840281255543</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0004719180869869888</v>
+        <v>0.0002179523726226762</v>
       </c>
       <c r="I13" t="n">
-        <v>8.168163185473531e-05</v>
+        <v>3.606350219342858e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001437266357243061</v>
+        <v>0.0003860432771034539</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004178228788077831</v>
+        <v>0.001354882027953863</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0004256664251442999</v>
+        <v>8.17976106191054e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.003948725759983063</v>
+        <v>0.0001373330742353573</v>
       </c>
       <c r="N13" t="n">
-        <v>0.001863379264250398</v>
+        <v>0.0003316932125017047</v>
       </c>
       <c r="O13" t="n">
-        <v>0.004915987141430378</v>
+        <v>0.0007813598494976759</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0004446032689884305</v>
+        <v>0.0006760554388165474</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0009018722339533269</v>
+        <v>0.0004047449328936636</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0002687832748051733</v>
+        <v>6.141881021903828e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0003993542632088065</v>
+        <v>0.0001614623906789348</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001163151813670993</v>
+        <v>0.0002122677979059517</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0003406528558116406</v>
+        <v>7.401865877909586e-05</v>
       </c>
       <c r="V13" t="n">
-        <v>0.000808826822321862</v>
+        <v>0.000280804670182988</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0006045338814146817</v>
+        <v>0.0002565430186223239</v>
       </c>
       <c r="X13" t="n">
-        <v>0.000419693416915834</v>
+        <v>3.748958624782972e-05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0005793782765977085</v>
+        <v>0.0001091651065507904</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001225354499183595</v>
+        <v>0.0003921553725376725</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0005525146261788905</v>
+        <v>0.0002183216711273417</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0001806472719181329</v>
+        <v>0.0003514091367833316</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.001059318543411791</v>
+        <v>8.29306518426165e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.00012907077325508</v>
+        <v>1.305188561673276e-05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0006451061926782131</v>
+        <v>1.753468677634373e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0006068485090509057</v>
+        <v>0.0001994738704524934</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.000540147942956537</v>
+        <v>0.0001758404396241531</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001031617051921785</v>
+        <v>0.0001542113022878766</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0002337299665668979</v>
+        <v>0.0004875967861153185</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6.196173490025103e-05</v>
+        <v>6.586319068446755e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0008222722681239247</v>
+        <v>0.0002046705631073564</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0008256791043095291</v>
+        <v>7.115522748790681e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.009544525411911e-05</v>
+        <v>3.411926081753336e-05</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0002716429298743606</v>
+        <v>0.0001546834828332067</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0002297936443937942</v>
+        <v>0.0002285728696733713</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0008432753966189921</v>
+        <v>3.375683081685565e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0006652464508078992</v>
+        <v>2.032380871241912e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.052039680071175e-05</v>
+        <v>0.0004010878619737923</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0007266003522090614</v>
+        <v>6.765859143342823e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001043282216414809</v>
+        <v>0.0002238150045741349</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.005230533424764872</v>
+        <v>0.00124968308955431</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.000154779088916257</v>
+        <v>0.0001518503704573959</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0004056895559187979</v>
+        <v>9.906812920235097e-06</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001030670828185976</v>
+        <v>0.0002049712493317202</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.00199162820354104</v>
+        <v>0.000953362206928432</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0006253575556911528</v>
+        <v>0.0001294907706324011</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001457010861486197</v>
+        <v>0.0001574885827722028</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0008128085755743086</v>
+        <v>0.0001473803276894614</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0007000387995503843</v>
+        <v>0.0002870307071134448</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0009113779524341226</v>
+        <v>0.0003876310947816819</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.001496950513683259</v>
+        <v>1.718882776913233e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.001703985966742039</v>
+        <v>0.0004702194419223815</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.002284280257299542</v>
+        <v>0.0002921896521002054</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.001594534027390182</v>
+        <v>0.0002403924590907991</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.2823729775846e-05</v>
+        <v>0.0003708833828568459</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.001998679945245385</v>
+        <v>0.0004715009999927133</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0001778486475814134</v>
+        <v>0.0001112663885578513</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001486286637373269</v>
+        <v>0.0001469725830247626</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.001645267591811717</v>
+        <v>0.0002884326968342066</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0006367264431901276</v>
+        <v>0.0001095684710890055</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.001898567541502416</v>
+        <v>0.0006899855798110366</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.001462108455598354</v>
+        <v>0.0004705067840404809</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.000383153441362083</v>
+        <v>0.0001394103019265458</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001060430891811848</v>
+        <v>0.0003085851494688541</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004588489537127316</v>
+        <v>0.0003829553897958249</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0003606911050155759</v>
+        <v>0.0001543302205391228</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0005025903810746968</v>
+        <v>0.0004133831826038659</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.002274592872709036</v>
+        <v>0.0006626598187722266</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0005321133648976684</v>
+        <v>0.0001492778392275795</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0001783907064236701</v>
+        <v>0.0001832496636779979</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0003810090420302004</v>
+        <v>0.0001221218408318236</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.000312383723212406</v>
+        <v>0.0003773873031605035</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.00107221701182425</v>
+        <v>8.870007877703756e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0008307347889058292</v>
+        <v>0.0001868722756626084</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0005243947962298989</v>
+        <v>6.396864773705602e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0001399817119818181</v>
+        <v>5.464153218781576e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.001169140450656414</v>
+        <v>0.0001625415170565248</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0006737303920090199</v>
+        <v>5.329271880327724e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0007789066294208169</v>
+        <v>5.195654739509337e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0004699379787780344</v>
+        <v>0.0001287148625124246</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0006714115152135491</v>
+        <v>0.0001882388023659587</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002032430638791993</v>
+        <v>6.756094808224589e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>5.532383511308581e-05</v>
+        <v>2.353343006689101e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0003466935595497489</v>
+        <v>9.742353540787008e-06</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.001277486560866237</v>
+        <v>0.0003125022631138563</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001023862976580858</v>
+        <v>0.000628410023637116</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0003087161458097398</v>
+        <v>0.0002907986927311867</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.000784296658821404</v>
+        <v>0.0004333932010922581</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0007230911869555712</v>
+        <v>0.0005155886174179614</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0002999241987708956</v>
+        <v>0.0002379465440753847</v>
       </c>
       <c r="CS13" t="n">
-        <v>6.910374213475734e-05</v>
+        <v>0.0002774897729977965</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0003759521059691906</v>
+        <v>0.0003877170966006815</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001051579747581854</v>
+        <v>6.496391142718494e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>4.221017661620863e-05</v>
+        <v>9.357614908367395e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0008676957222633064</v>
+        <v>0.00014918674423825</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0007221896667033434</v>
+        <v>2.258743916172534e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.001112361089326441</v>
+        <v>0.0001307958737015724</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0003300897369626909</v>
+        <v>0.0001072045706678182</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0006045777117833495</v>
+        <v>0.0001592304324731231</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0003318173694424331</v>
+        <v>0.0001113443140638992</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.000491530925501138</v>
+        <v>3.51254602719564e-05</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.000223427647142671</v>
+        <v>5.156846236786805e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0007874915609136224</v>
+        <v>0.0001973087200894952</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.002180929761379957</v>
+        <v>7.512563024647534e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>9.027276973938569e-05</v>
+        <v>0.0001645316515350714</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.00165888003539294</v>
+        <v>0.0004424781072884798</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0004576408537104726</v>
+        <v>1.394938954035752e-05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>4.495637404033914e-05</v>
+        <v>3.069941521971487e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001764827058650553</v>
+        <v>0.0001810151588870212</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0008496122900396585</v>
+        <v>0.0001969866862054914</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0005878197262063622</v>
+        <v>0.000182635456440039</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.00069260667078197</v>
+        <v>9.636512004362885e-06</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.000743535696528852</v>
+        <v>0.0003000931756105274</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0007401409093290567</v>
+        <v>2.444429992465302e-05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0008584993192926049</v>
+        <v>6.022414163453504e-05</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0004856356827076524</v>
+        <v>8.017077198019251e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>2.832355676218867e-06</v>
+        <v>6.888869393151253e-05</v>
       </c>
       <c r="DT13" t="n">
-        <v>3.023282624781132e-05</v>
+        <v>5.312235953169875e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0001498249039286748</v>
+        <v>0.0007075613830238581</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0004242083232384175</v>
+        <v>4.503359377849847e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>5.855901690665632e-05</v>
+        <v>0.000188754391274415</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.831397619564086e-05</v>
+        <v>0.0002649340021889657</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001069061807356775</v>
+        <v>0.0001517444616183639</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0003051085222978145</v>
+        <v>0.0001600083633093163</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0003696767962537706</v>
+        <v>8.592792437411845e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0001274843234568834</v>
+        <v>8.538409929315094e-06</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0003151221899315715</v>
+        <v>0.0003651282750070095</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0001993761397898197</v>
+        <v>0.0001714943937258795</v>
       </c>
       <c r="EE13" t="n">
-        <v>6.330030737444758e-05</v>
+        <v>5.855035851709545e-06</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0004530579899437726</v>
+        <v>0.0001710950309643522</v>
       </c>
       <c r="EG13" t="n">
-        <v>5.341511132428423e-05</v>
+        <v>1.617037924006581e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0002694441354833543</v>
+        <v>8.494524081470445e-05</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0005600853473879397</v>
+        <v>8.352327131433412e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001632783678360283</v>
+        <v>0.0001296138216275722</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0004160098324064165</v>
+        <v>3.291697066742927e-05</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0005672646220773458</v>
+        <v>7.430519872286823e-06</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001754608092596754</v>
+        <v>5.465678623295389e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>6.567037780769169e-05</v>
+        <v>5.830670124851167e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.000718386028893292</v>
+        <v>0.0003354290674906224</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.000270275108050555</v>
+        <v>0.0002582800516393036</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0005843052640557289</v>
+        <v>0.0001696497056400403</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0006600114866159856</v>
+        <v>7.789070514263585e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0006124961655586958</v>
+        <v>0.0003159354091621935</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001180006423965096</v>
+        <v>6.533791747642681e-06</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0004548736033029854</v>
+        <v>0.0002032751363003626</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0006779560353606939</v>
+        <v>0.0003059906011912972</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0002722191857174039</v>
+        <v>7.799616287229583e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>8.369580609723926e-05</v>
+        <v>0.0001158160011982545</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0007680284325033426</v>
+        <v>0.0002078035176964477</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0005056474474258721</v>
+        <v>4.613532655639574e-05</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0007854312425479293</v>
+        <v>0.0001125184353441</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004331189556978643</v>
+        <v>9.925467747962102e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0006202966324053705</v>
+        <v>0.0002105831372318789</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0004566387797240168</v>
+        <v>1.721185617498122e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0001105151677620597</v>
+        <v>8.038539817789569e-05</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0004889773554168642</v>
+        <v>4.819509194931015e-05</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0005087749450467527</v>
+        <v>0.000191736122360453</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0007486384711228311</v>
+        <v>9.786414011614397e-06</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0007027160027064383</v>
+        <v>5.774924284196459e-05</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0002484297438059002</v>
+        <v>0.0004656169912777841</v>
       </c>
       <c r="FK13" t="n">
-        <v>1.502774830441922e-05</v>
+        <v>0.0003937959845643491</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0003865359467454255</v>
+        <v>0.0002244508359581232</v>
       </c>
       <c r="FM13" t="n">
-        <v>9.175761078950018e-06</v>
+        <v>0.0002467367448844016</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001201002887682989</v>
+        <v>0.0003317260416224599</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.000250246113864705</v>
+        <v>1.053351570590166e-05</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0008692223345860839</v>
+        <v>0.000471696286695078</v>
       </c>
       <c r="FQ13" t="n">
-        <v>4.260882269591093e-05</v>
+        <v>0.0005225890781730413</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0001389201352139935</v>
+        <v>0.0002620499581098557</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.00107775698415935</v>
+        <v>0.0002209218655480072</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.002603146946057677</v>
+        <v>0.001442713895812631</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0007215451914817095</v>
+        <v>0.0002262477355543524</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.000481904367916286</v>
+        <v>0.00024175297585316</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0009135511936619878</v>
+        <v>0.0002529755583964288</v>
       </c>
       <c r="FX13" t="n">
-        <v>1.241298741661012e-05</v>
+        <v>4.28974162787199e-05</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0007598269730806351</v>
+        <v>5.807699199067429e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.001005221041850746</v>
+        <v>0.0001415795413777232</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0003353733918629587</v>
+        <v>0.0001084904142771848</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0009864370804280043</v>
+        <v>0.0004186417791061103</v>
       </c>
       <c r="GC13" t="n">
-        <v>7.791006646584719e-05</v>
+        <v>0.0001099678993341513</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0004984478582628071</v>
+        <v>3.229143476346508e-05</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.00221250532194972</v>
+        <v>0.0001940751681104302</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.001294021727517247</v>
+        <v>0.0001932182349264622</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0003889563377015293</v>
+        <v>0.000183907977771014</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.004745980724692345</v>
+        <v>0.0216807946562767</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003508965950459242</v>
+        <v>0.0198864359408617</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01112652476876974</v>
+        <v>0.075728639960289</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01136132702231407</v>
+        <v>0.02325969934463501</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002743377117440104</v>
+        <v>0.008456047624349594</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001411631819792092</v>
+        <v>0.02709967084228992</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001384332310408354</v>
+        <v>0.001067671924829483</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0032721480820328</v>
+        <v>0.03739482536911964</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001504580024629831</v>
+        <v>0.0243847481906414</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006272776518017054</v>
+        <v>0.01124803815037012</v>
       </c>
       <c r="K14" t="n">
-        <v>0.003166417591273785</v>
+        <v>0.01287195831537247</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008642925880849361</v>
+        <v>0.06941457092761993</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01135460566729307</v>
+        <v>0.01870037242770195</v>
       </c>
       <c r="N14" t="n">
-        <v>0.00345791969448328</v>
+        <v>0.009045751765370369</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001568628358654678</v>
+        <v>0.02307089045643806</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0007061869837343693</v>
+        <v>0.007144441828131676</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.004172362387180328</v>
+        <v>0.03955161198973656</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001099521876312792</v>
+        <v>0.02028116770088673</v>
       </c>
       <c r="S14" t="n">
-        <v>0.003167235758155584</v>
+        <v>0.000188357662409544</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0006292512989602983</v>
+        <v>0.009684596210718155</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0002196168643422425</v>
+        <v>0.008860284462571144</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0002356582845095545</v>
+        <v>0.01740632019937038</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001518812379799783</v>
+        <v>0.00658395467326045</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0005812982562929392</v>
+        <v>0.01247104909271002</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.001141737098805606</v>
+        <v>0.007122683338820934</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.004221337847411633</v>
+        <v>0.003547155298292637</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.768178819678724e-05</v>
+        <v>0.009933155030012131</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001368229277431965</v>
+        <v>0.005912174470722675</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.001687646843492985</v>
+        <v>0.006249420810490847</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0002478132373653352</v>
+        <v>0.0133318705484271</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.003276519477367401</v>
+        <v>0.02668123319745064</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.002245152601972222</v>
+        <v>0.01509886234998703</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001147350194514729</v>
+        <v>0.003221153514459729</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.000350463145878166</v>
+        <v>0.004417532123625278</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001385836396366358</v>
+        <v>0.01258014142513275</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0001007088285405189</v>
+        <v>0.01909744553267956</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0004557481152005494</v>
+        <v>0.0009165913215838373</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.001923216506838799</v>
+        <v>0.009035896509885788</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0007447208045050502</v>
+        <v>0.01213591173291206</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0009471155935898423</v>
+        <v>0.0148350466042757</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0006485898047685623</v>
+        <v>0.01688176766037941</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.001344734453596175</v>
+        <v>0.02034694515168667</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.002007872331887484</v>
+        <v>0.00797903910279274</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.000479257432743907</v>
+        <v>0.006089182570576668</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0009718709043227136</v>
+        <v>0.0006859658751636744</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0003802625287789851</v>
+        <v>0.01207076758146286</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001404750277288258</v>
+        <v>0.005992998369038105</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.006568947806954384</v>
+        <v>0.04712381586432457</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.009373058564960957</v>
+        <v>0.03457629308104515</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.001417348277755082</v>
+        <v>0.02048197574913502</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.00320254429243505</v>
+        <v>0.0336628369987011</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.001168709481135011</v>
+        <v>0.02310221083462238</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.004193644504994154</v>
+        <v>0.01255715638399124</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.001804391387850046</v>
+        <v>0.009960582479834557</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.006771685555577278</v>
+        <v>0.02673221006989479</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.002169118728488684</v>
+        <v>0.000720213633030653</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0009804383153095841</v>
+        <v>0.009873387403786182</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.001487159170210361</v>
+        <v>0.03480138629674911</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.005952591542154551</v>
+        <v>0.02214605733752251</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.001086286036297679</v>
+        <v>0.02005724050104618</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.004291389137506485</v>
+        <v>0.01115110795944929</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.00750832911580801</v>
+        <v>0.01929637044668198</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0006711359019391239</v>
+        <v>0.0076716891489923</v>
       </c>
       <c r="BL14" t="n">
-        <v>4.954577889293432e-05</v>
+        <v>0.001989470794796944</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001705289701931179</v>
+        <v>0.005803987383842468</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.002868551760911942</v>
+        <v>0.0118001876398921</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.002141440752893686</v>
+        <v>0.001146538648754358</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.00350791378878057</v>
+        <v>0.01721106469631195</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0007261065184138715</v>
+        <v>0.007836502976715565</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.002363522304221988</v>
+        <v>0.00470465375110507</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.001099553541280329</v>
+        <v>0.002713195513933897</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.002485297620296478</v>
+        <v>0.00538388267159462</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0008605004986748099</v>
+        <v>0.001828972133807838</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.001652081264182925</v>
+        <v>0.01712062582373619</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.003802027320489287</v>
+        <v>0.02661626227200031</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.004579913802444935</v>
+        <v>0.04818923771381378</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0007123987306840718</v>
+        <v>0.004326358437538147</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.000627119850832969</v>
+        <v>0.009168725460767746</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.00188796641305089</v>
+        <v>0.01461085304617882</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.005124984309077263</v>
+        <v>0.001493489020504057</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.001826583291403949</v>
+        <v>0.007692951709032059</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.001154870493337512</v>
+        <v>0.0008016804349608719</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001433210680261254</v>
+        <v>0.01390369981527328</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.002548787742853165</v>
+        <v>0.01779410429298878</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.002141994656994939</v>
+        <v>0.004133723210543394</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.001066495082341135</v>
+        <v>0.000284798676148057</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0009107374353334308</v>
+        <v>0.003567173378542066</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0009639877825975418</v>
+        <v>0.001026614452712238</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0008891290053725243</v>
+        <v>0.004215121269226074</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.001700180931948125</v>
+        <v>0.005626784637570381</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.003327313344925642</v>
+        <v>0.001893648877739906</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.001048854901455343</v>
+        <v>0.0225212424993515</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.00015304668340832</v>
+        <v>0.002766092075034976</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.001134353107772768</v>
+        <v>0.006378751248121262</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0007728040800429881</v>
+        <v>0.03074858337640762</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.002298661973327398</v>
+        <v>0.001538306009024382</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.001437416300177574</v>
+        <v>0.004756227135658264</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.00271713687106967</v>
+        <v>0.0005271722911857069</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.001284633879549801</v>
+        <v>0.01141498517245054</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.001236941432580352</v>
+        <v>0.002437743358314037</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0007211234769783914</v>
+        <v>0.007105287164449692</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.001603104290552437</v>
+        <v>0.01701231859624386</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.001563293044455349</v>
+        <v>0.004270322620868683</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.001169811584986746</v>
+        <v>0.002694061491638422</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.000784457428380847</v>
+        <v>0.006637913640588522</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0005707286763936281</v>
+        <v>0.003212614916265011</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0004063549567945302</v>
+        <v>0.001352515304461122</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.001714923186227679</v>
+        <v>0.007906200364232063</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001046039978973567</v>
+        <v>0.007535495329648256</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.00750203849747777</v>
+        <v>0.0009175688028335571</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0004345099441707134</v>
+        <v>0.04323361814022064</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001941944239661098</v>
+        <v>0.004013661295175552</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0001136424107244238</v>
+        <v>0.02147713303565979</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.005378894042223692</v>
+        <v>0.0113402372226119</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.007193757686764002</v>
+        <v>0.01535011455416679</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0006864985916763544</v>
+        <v>0.00790123175829649</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001767753856256604</v>
+        <v>0.02231358736753464</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0006579856853932142</v>
+        <v>0.008677415549755096</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.001986523624509573</v>
+        <v>0.001854472910054028</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.002579196821898222</v>
+        <v>0.003101957961916924</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0004674035881180316</v>
+        <v>0.003940531983971596</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.002337700920179486</v>
+        <v>0.01098922174423933</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0001996969804167747</v>
+        <v>0.004724540747702122</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.001273067784495652</v>
+        <v>0.01390069164335728</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.001549768378026783</v>
+        <v>0.001425786409527063</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.002077425364404917</v>
+        <v>0.004530672449618578</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0007392648840323091</v>
+        <v>0.01301750633865595</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.001337577821686864</v>
+        <v>0.003829672001302242</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0005359018687158823</v>
+        <v>0.000939955236390233</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.00192733877338469</v>
+        <v>0.002878263825550675</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0005613098619505763</v>
+        <v>0.01009934954345226</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.002916166558861732</v>
+        <v>0.02413102053105831</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0009467609925195575</v>
+        <v>0.008541710674762726</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.00277356430888176</v>
+        <v>0.003027867991477251</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.000548205163795501</v>
+        <v>0.00400112010538578</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.001310722203925252</v>
+        <v>0.004540212452411652</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0008722735801711679</v>
+        <v>0.005709245335310698</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.002482560696080327</v>
+        <v>0.01223852764815092</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.003037175163626671</v>
+        <v>0.001490969443693757</v>
       </c>
       <c r="EJ14" t="n">
-        <v>9.034459799295291e-05</v>
+        <v>0.004019016399979591</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0002574730897322297</v>
+        <v>9.842263534665108e-05</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0007270576898008585</v>
+        <v>0.002776373876258731</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0008599237189628184</v>
+        <v>0.00613080570474267</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.002681650454178452</v>
+        <v>0.001938334666192532</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.001309953047893941</v>
+        <v>0.003208332462236285</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0006630508578382432</v>
+        <v>0.01633579656481743</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.001759825507178903</v>
+        <v>0.005396280903369188</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0006957834120839834</v>
+        <v>0.003798673860728741</v>
       </c>
       <c r="ES14" t="n">
-        <v>9.848138870438561e-05</v>
+        <v>0.007737293373793364</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0007432421552948654</v>
+        <v>0.01990656927227974</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0001221965503646061</v>
+        <v>0.003356612287461758</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.004301280248910189</v>
+        <v>0.007525875233113766</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.002921550069004297</v>
+        <v>0.004115810617804527</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.001124256523326039</v>
+        <v>0.0005116070387884974</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0008761177305132151</v>
+        <v>0.01516883354634047</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.002031102310866117</v>
+        <v>0.01717214100062847</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.00153514149133116</v>
+        <v>0.00471805315464735</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0009101474424824119</v>
+        <v>0.002283843467012048</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.001305451733060181</v>
+        <v>0.009213242679834366</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0003303181729279459</v>
+        <v>0.003096206579357386</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0003410995996091515</v>
+        <v>2.359552308917046e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.002092983806505799</v>
+        <v>0.007087877485901117</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0002885099675040692</v>
+        <v>0.0009515595156699419</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.001868123770691454</v>
+        <v>0.002571101533249021</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0008781810756772757</v>
+        <v>0.02697969600558281</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.002440918004140258</v>
+        <v>0.008186724036931992</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.001090448698960245</v>
+        <v>0.01620102673768997</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0007146964780986309</v>
+        <v>0.0213228203356266</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.00150820764247328</v>
+        <v>0.003459175815805793</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.00101121561601758</v>
+        <v>0.006951251067221165</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.001732982345856726</v>
+        <v>0.005708165001124144</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.003967606462538242</v>
+        <v>0.002465929137542844</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.002056091791018844</v>
+        <v>0.001824000384658575</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.006704776547849178</v>
+        <v>0.008276124484837055</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.003182624001055956</v>
+        <v>0.02102563343942165</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0005514348158612847</v>
+        <v>0.004913624841719866</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.002009633928537369</v>
+        <v>0.01939808949828148</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0006783544085919857</v>
+        <v>0.01945342123508453</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0008321734494529665</v>
+        <v>0.01979921758174896</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.001536656985990703</v>
+        <v>0.01805555447936058</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0009681606898084283</v>
+        <v>0.0006452522939071059</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.001443008193746209</v>
+        <v>0.03024554997682571</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.003022783435881138</v>
+        <v>0.01618272811174393</v>
       </c>
       <c r="GB14" t="n">
-        <v>8.851816528476775e-05</v>
+        <v>0.009741628542542458</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.002715733600780368</v>
+        <v>0.001057128538377583</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.003201938001438975</v>
+        <v>0.007713973056524992</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0003145762602798641</v>
+        <v>0.005986922886222601</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.001307276543229818</v>
+        <v>0.01725712604820728</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0007910589338280261</v>
+        <v>0.008460217155516148</v>
       </c>
     </row>
     <row r="15">
@@ -8965,1140 +8965,1140 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.004291648976504803</v>
+        <v>0.005505213979631662</v>
       </c>
       <c r="B16" t="n">
-        <v>0.07614853978157043</v>
+        <v>0.009912341833114624</v>
       </c>
       <c r="C16" t="n">
-        <v>0.005316010676324368</v>
+        <v>0.009344921447336674</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02183685451745987</v>
+        <v>0.0006667436100542545</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04060430452227592</v>
+        <v>0.009043071419000626</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02127567306160927</v>
+        <v>0.02434548735618591</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00961894728243351</v>
+        <v>0.0007876443560235202</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01097032334655523</v>
+        <v>0.01153167244046926</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003475972451269627</v>
+        <v>0.0005535091040655971</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004256070591509342</v>
+        <v>0.001126340124756098</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06130330637097359</v>
+        <v>0.02150349505245686</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003701051697134972</v>
+        <v>0.006073950324207544</v>
       </c>
       <c r="M16" t="n">
-        <v>0.009200782515108585</v>
+        <v>0.00195839861407876</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03128543496131897</v>
+        <v>0.0122934989631176</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02366643399000168</v>
+        <v>0.02776449918746948</v>
       </c>
       <c r="P16" t="n">
-        <v>0.008789031766355038</v>
+        <v>0.004746320657432079</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.004205838777124882</v>
+        <v>0.0006605559028685093</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0009585029329173267</v>
+        <v>0.003396276850253344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0009653079905547202</v>
+        <v>0.00441961083561182</v>
       </c>
       <c r="T16" t="n">
-        <v>0.008552908897399902</v>
+        <v>0.001060322276316583</v>
       </c>
       <c r="U16" t="n">
-        <v>0.002527835313230753</v>
+        <v>0.003241288941353559</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01434377208352089</v>
+        <v>0.002926198998466134</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01758107542991638</v>
+        <v>0.002810732461512089</v>
       </c>
       <c r="X16" t="n">
-        <v>0.006641648709774017</v>
+        <v>0.003971239551901817</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.001230521709658206</v>
+        <v>0.001580801210366189</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.01030639931559563</v>
+        <v>0.006799731403589249</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0001500945072621107</v>
+        <v>0.002752552507445216</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.003605050500482321</v>
+        <v>0.01076680049300194</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.01079303957521915</v>
+        <v>2.967496402561665e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.00200793263502419</v>
+        <v>0.001672476064413786</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0001670214114710689</v>
+        <v>0.007797517813742161</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.006162876728922129</v>
+        <v>0.008893288671970367</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.002489887410774827</v>
+        <v>0.004580831155180931</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.01058171410113573</v>
+        <v>0.005642827600240707</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.001515589538030326</v>
+        <v>0.01123892143368721</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.004616556223481894</v>
+        <v>0.0006072011310607195</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.01089840196073055</v>
+        <v>0.00368402386084199</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.009122030809521675</v>
+        <v>0.004076163284480572</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.003814588999375701</v>
+        <v>0.001893586479127407</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.001470444491133094</v>
+        <v>0.003574807196855545</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.01302653644233942</v>
+        <v>0.006236575078219175</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.009223099797964096</v>
+        <v>7.338961586356163e-05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.006435495335608721</v>
+        <v>0.002855896949768066</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0005811579758301377</v>
+        <v>0.008253218606114388</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.002643316052854061</v>
+        <v>0.001456774072721601</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.01120006572455168</v>
+        <v>0.0004596310900524259</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.06131560355424881</v>
+        <v>0.02332665026187897</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0009593130089342594</v>
+        <v>0.0006734386552125216</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.001823446713387966</v>
+        <v>0.000534845283254981</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.01290015503764153</v>
+        <v>0.001799062127247453</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.01480355206876993</v>
+        <v>0.01842552982270718</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.01104509085416794</v>
+        <v>0.0008612714009359479</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.008351610042154789</v>
+        <v>0.00097717868629843</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.00739777460694313</v>
+        <v>0.002437452087178826</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.003616366535425186</v>
+        <v>0.00455261766910553</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.02848353236913681</v>
+        <v>0.001526143751107156</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.009543486870825291</v>
+        <v>0.002325812354683876</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.004074057564139366</v>
+        <v>0.002519539324566722</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.02605319023132324</v>
+        <v>0.001531627494841814</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0136001268401742</v>
+        <v>0.003450767369940877</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.001796363852918148</v>
+        <v>0.003518235636875033</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.01081238500773907</v>
+        <v>0.00825989618897438</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.004522529430687428</v>
+        <v>0.003802240360528231</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.01167380437254906</v>
+        <v>0.001822282560169697</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03487251326441765</v>
+        <v>0.01365857757627964</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.002471164800226688</v>
+        <v>9.739212691783905e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.003033900167793036</v>
+        <v>0.004309805110096931</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.01985886879265308</v>
+        <v>0.01039467286318541</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01074675843119621</v>
+        <v>0.00673522986471653</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.007756428327411413</v>
+        <v>0.008006761781871319</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.002843939000740647</v>
+        <v>0.003759983461350203</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0007792824180796742</v>
+        <v>0.00415309751406312</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.004518546629697084</v>
+        <v>0.003363365773111582</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.03323633223772049</v>
+        <v>0.01123351510614157</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.01124447118490934</v>
+        <v>0.001274805748835206</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.003319083945825696</v>
+        <v>0.003564568236470222</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.002029526978731155</v>
+        <v>0.00162839237600565</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.005849696695804596</v>
+        <v>0.004730595275759697</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.003864144673570991</v>
+        <v>0.001190892187878489</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.002598205581307411</v>
+        <v>0.00220636697486043</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.002705378457903862</v>
+        <v>0.0007266529137268662</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.002881271066144109</v>
+        <v>0.002974027534946799</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.01060042437165976</v>
+        <v>0.003179457038640976</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.002290830248966813</v>
+        <v>0.001975207356736064</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.004768888000398874</v>
+        <v>9.498652070760727e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.002974884584546089</v>
+        <v>0.003178096143528819</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.003205195534974337</v>
+        <v>0.007297355215996504</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.005654723383486271</v>
+        <v>0.002517371438443661</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.002778851427137852</v>
+        <v>0.0002126773470081389</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0006878533167764544</v>
+        <v>0.0008856090717017651</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.01964759081602097</v>
+        <v>0.002181641524657607</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.02389253303408623</v>
+        <v>0.01546759251505136</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.0009923100005835295</v>
+        <v>0.004612493328750134</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.007195455953478813</v>
+        <v>0.002937762532383204</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.01246400829404593</v>
+        <v>0.006550608202815056</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0003338283859193325</v>
+        <v>0.003620848525315523</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.002616804325953126</v>
+        <v>0.002088770037516952</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.002996856346726418</v>
+        <v>0.0008535365341231227</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.004119737073779106</v>
+        <v>0.003631669096648693</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.002438527764752507</v>
+        <v>0.001978107495233417</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.007254877127707005</v>
+        <v>0.002652042079716921</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.003699162509292364</v>
+        <v>0.0006297677755355835</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.00803699716925621</v>
+        <v>0.001304297707974911</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.00156030326616019</v>
+        <v>0.002145510632544756</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.002847344148904085</v>
+        <v>0.007940755225718021</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.005037569440901279</v>
+        <v>0.0002831550955306739</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.003874323796480894</v>
+        <v>0.0003543307539075613</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.001203785301186144</v>
+        <v>0.0008059717947617173</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0004674163646996021</v>
+        <v>0.0003439821302890778</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.007185455877333879</v>
+        <v>0.006671159062534571</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.005327568855136633</v>
+        <v>0.005377663299441338</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.04704684391617775</v>
+        <v>0.004392439965158701</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.006121406331658363</v>
+        <v>0.003320349613204598</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.003823262173682451</v>
+        <v>0.0008426630520261824</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.01306955143809319</v>
+        <v>0.005448108538985252</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0007197326049208641</v>
+        <v>0.004280811175704002</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.008530363440513611</v>
+        <v>0.003196044825017452</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.008069658651947975</v>
+        <v>0.002800496062263846</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.008440154604613781</v>
+        <v>0.001853947062045336</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.01213463768362999</v>
+        <v>0.001578245311975479</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.006096439436078072</v>
+        <v>0.007853981107473373</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.00531566608697176</v>
+        <v>0.007486033253371716</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.004518904723227024</v>
+        <v>0.002893021795898676</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.001973031554371119</v>
+        <v>0.000794142484664917</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.001161026302725077</v>
+        <v>0.005794454365968704</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.005045940633863211</v>
+        <v>0.001763464300893247</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.006399485748261213</v>
+        <v>0.002120494842529297</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.006254274863749743</v>
+        <v>0.002122426172718406</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.005293203983455896</v>
+        <v>0.002264149021357298</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.00104412017390132</v>
+        <v>0.0039464863948524</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.00044294074177742</v>
+        <v>0.004471694584935904</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.003072201739996672</v>
+        <v>0.006207086145877838</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.002294314559549093</v>
+        <v>0.002401416189968586</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.005963527597486973</v>
+        <v>0.0007782329339534044</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.001604481833055615</v>
+        <v>0.004564235918223858</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.002641367726027966</v>
+        <v>0.003994242288172245</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.005027728620916605</v>
+        <v>0.003534256480634212</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0009022934245876968</v>
+        <v>0.003270330373197794</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.003403755836188793</v>
+        <v>0.0001413374557159841</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.004677615128457546</v>
+        <v>0.001114870305173099</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.002269569784402847</v>
+        <v>0.009437987580895424</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.005490719806402922</v>
+        <v>0.001112175174057484</v>
       </c>
       <c r="EM16" t="n">
-        <v>5.246629007160664e-05</v>
+        <v>0.001460946747101843</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.000102766789495945</v>
+        <v>0.0004972222959622741</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.01255717594176531</v>
+        <v>0.00380053254775703</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.004025742411613464</v>
+        <v>4.101498052477837e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.007475042715668678</v>
+        <v>0.004613740369677544</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.01045502256602049</v>
+        <v>0.005346701014786959</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.00452593294903636</v>
+        <v>0.003696809755638242</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.008636606857180595</v>
+        <v>0.001090947072952986</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.003935971762984991</v>
+        <v>0.001441953354515135</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.01041263528168201</v>
+        <v>0.0002007676521316171</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.001607837271876633</v>
+        <v>0.001531124231405556</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.002047221641987562</v>
+        <v>0.002543442882597446</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.005746032111346722</v>
+        <v>0.004293453879654408</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.001972031546756625</v>
+        <v>0.001641116105020046</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.003758846782147884</v>
+        <v>5.309702828526497e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.003086317330598831</v>
+        <v>0.001928627025336027</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.005760172847658396</v>
+        <v>0.006474386900663376</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.007208008319139481</v>
+        <v>0.002187812002375722</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.002767494414001703</v>
+        <v>0.0003643278614617884</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0008270188118331134</v>
+        <v>0.0002099263947457075</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.001116106286644936</v>
+        <v>0.0004026145907118917</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.009564911015331745</v>
+        <v>0.004426103085279465</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.002076775068417192</v>
+        <v>0.003219040110707283</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.008688956499099731</v>
+        <v>0.007481948938220739</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.007020801771432161</v>
+        <v>0.001509365858510137</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0063466583378613</v>
+        <v>0.001808657078072429</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.006857836153358221</v>
+        <v>0.002725557889789343</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.001146133523434401</v>
+        <v>0.006668242160230875</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.003156080143526196</v>
+        <v>0.003656458109617233</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0182024147361517</v>
+        <v>0.000796270789578557</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.002809512661769986</v>
+        <v>0.003325665602460504</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.008415217511355877</v>
+        <v>0.006973338313400745</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.005425000563263893</v>
+        <v>0.0008336220635101199</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.007088025100529194</v>
+        <v>0.001070838537998497</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.006360067054629326</v>
+        <v>0.0007631802000105381</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.004690460860729218</v>
+        <v>0.002023971872404218</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0009021464502438903</v>
+        <v>0.01118590030819178</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.007045084610581398</v>
+        <v>0.004582830704748631</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.01229327823966742</v>
+        <v>0.003221426159143448</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.01143160834908485</v>
+        <v>0.003779734950512648</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.006637595593929291</v>
+        <v>0.002427480882033706</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.001000254182145</v>
+        <v>5.361245712265372e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.001139408792369068</v>
+        <v>0.007749399170279503</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.01637857593595982</v>
+        <v>0.007016613148152828</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.01273428183048964</v>
+        <v>0.0004758492286782712</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.003122302005067468</v>
+        <v>0.004631869960576296</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.003085733158513904</v>
+        <v>0.001887664431706071</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0004143056576140225</v>
+        <v>0.04091307520866394</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01894703879952431</v>
+        <v>0.2137939631938934</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002730022417381406</v>
+        <v>0.01901485584676266</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0127438697963953</v>
+        <v>0.2861091792583466</v>
       </c>
       <c r="E17" t="n">
-        <v>0.007956280373036861</v>
+        <v>0.007952260784804821</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001316843088716269</v>
+        <v>0.04288726672530174</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003963831812143326</v>
+        <v>0.1359492093324661</v>
       </c>
       <c r="H17" t="n">
-        <v>0.002745423465967178</v>
+        <v>0.06297957897186279</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000689624052029103</v>
+        <v>0.02524893544614315</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0004582373658195138</v>
+        <v>0.03220541030168533</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01431068126112223</v>
+        <v>0.188165694475174</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0002239497116534039</v>
+        <v>0.0323474332690239</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01036118157207966</v>
+        <v>0.3674338161945343</v>
       </c>
       <c r="N17" t="n">
-        <v>0.008824232034385204</v>
+        <v>0.04481808841228485</v>
       </c>
       <c r="O17" t="n">
-        <v>0.003737324615940452</v>
+        <v>0.0537230484187603</v>
       </c>
       <c r="P17" t="n">
-        <v>0.003484122455120087</v>
+        <v>0.1101501509547234</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.001033908105455339</v>
+        <v>0.07665473967790604</v>
       </c>
       <c r="R17" t="n">
-        <v>0.001952418708242476</v>
+        <v>0.02698347717523575</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0005726731615141034</v>
+        <v>0.01988478004932404</v>
       </c>
       <c r="T17" t="n">
-        <v>0.003711060620844364</v>
+        <v>0.08276636153459549</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0007971688755787909</v>
+        <v>0.03432728350162506</v>
       </c>
       <c r="V17" t="n">
-        <v>0.002088733715936542</v>
+        <v>0.04147238284349442</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0007787046488374472</v>
+        <v>0.0621582418680191</v>
       </c>
       <c r="X17" t="n">
-        <v>0.002332970965653658</v>
+        <v>0.07466387748718262</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.002233752980828285</v>
+        <v>0.02146470919251442</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.002012343611568213</v>
+        <v>0.01706978306174278</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.001848484273068607</v>
+        <v>0.006125986576080322</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0004749201470986009</v>
+        <v>0.05337721854448318</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.002541914815083146</v>
+        <v>0.06096969544887543</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0009328324813395739</v>
+        <v>0.004702711943536997</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.00126810057554394</v>
+        <v>0.1199981719255447</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.001164189889095724</v>
+        <v>0.07359598577022552</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.00108318857382983</v>
+        <v>0.05883502587676048</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.002103989711031318</v>
+        <v>0.04856324195861816</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.00078593660145998</v>
+        <v>0.009594805538654327</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.001307176193222404</v>
+        <v>0.09264632314443588</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0007984195835888386</v>
+        <v>0.02010557428002357</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.003263428341597319</v>
+        <v>0.09447898715734482</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0007305124308913946</v>
+        <v>0.03065121360123158</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0001683358859736472</v>
+        <v>0.08839790523052216</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.001468558330088854</v>
+        <v>0.03881034255027771</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.00178444292396307</v>
+        <v>0.07898734509944916</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.001698908861726522</v>
+        <v>0.04291032254695892</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.001692630350589752</v>
+        <v>0.01329845003783703</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0008091133204288781</v>
+        <v>0.004903902765363455</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.00189244607463479</v>
+        <v>0.0335596464574337</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.01380835846066475</v>
+        <v>0.1767973154783249</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.001472327508963645</v>
+        <v>0.01563645899295807</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.002253938000649214</v>
+        <v>0.1203028708696365</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.002448357408866286</v>
+        <v>0.1553224474191666</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0003370319900568575</v>
+        <v>0.01154848467558622</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.00153275253251195</v>
+        <v>0.001750855706632137</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.001160869025625288</v>
+        <v>0.04759669303894043</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.737221262184903e-05</v>
+        <v>0.05111412703990936</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0008019386441446841</v>
+        <v>0.0732053741812706</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.00326509540900588</v>
+        <v>0.004240657668560743</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.003012493951246142</v>
+        <v>0.003380339127033949</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.004135034047067165</v>
+        <v>0.03682213649153709</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.006541213486343622</v>
+        <v>0.003108516335487366</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0007915892056189477</v>
+        <v>0.0226929672062397</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.002775652566924691</v>
+        <v>0.04929002001881599</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.001568559906445444</v>
+        <v>0.05820037797093391</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0010992840398103</v>
+        <v>0.09749524295330048</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.00264706090092659</v>
+        <v>0.001433419063687325</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.004091044887900352</v>
+        <v>0.01159658003598452</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.002427505562081933</v>
+        <v>0.006276675965636969</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0004423930367920548</v>
+        <v>0.02848608233034611</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.002094315597787499</v>
+        <v>0.03103489615023136</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.001847609179094434</v>
+        <v>0.012075399979949</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0004975730553269386</v>
+        <v>0.0118824727833271</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0007841807091608644</v>
+        <v>0.003792342264205217</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0007548155845142901</v>
+        <v>0.01225118432193995</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.002120373770594597</v>
+        <v>0.06700959056615829</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.008284459821879864</v>
+        <v>0.1677188277244568</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.003211807459592819</v>
+        <v>0.0230463445186615</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.00229471200145781</v>
+        <v>0.1393602788448334</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0007073840242810547</v>
+        <v>0.05353035405278206</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.002178536262363195</v>
+        <v>0.07909556478261948</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.001436538062989712</v>
+        <v>0.03594488278031349</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.001143384142778814</v>
+        <v>0.02479410171508789</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.002055331831797957</v>
+        <v>0.02928975969552994</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0005018889787606895</v>
+        <v>0.009322464466094971</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.002935984171926975</v>
+        <v>0.05376041680574417</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0009837702382355928</v>
+        <v>0.01565088704228401</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.001639197929762304</v>
+        <v>0.1119140982627869</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0002404222905170172</v>
+        <v>0.01132199261337519</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0009451226214878261</v>
+        <v>0.0214772392064333</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0008694078424014151</v>
+        <v>0.0003454652614891529</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0002457860100548714</v>
+        <v>0.03348040208220482</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0007859347970224917</v>
+        <v>0.01595785468816757</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.003468470415100455</v>
+        <v>0.03013327158987522</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.001965688774362206</v>
+        <v>0.08651949465274811</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0001477203913964331</v>
+        <v>0.02757273614406586</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.001380785135552287</v>
+        <v>0.2220068275928497</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.001625489792786539</v>
+        <v>0.107120968401432</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0001044533273670822</v>
+        <v>0.01954825781285763</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.002492205239832401</v>
+        <v>0.01876412332057953</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.00362962600775063</v>
+        <v>0.01341903209686279</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0006629892741329968</v>
+        <v>0.05120430514216423</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0005896052462048829</v>
+        <v>0.002659750171005726</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.002243354683741927</v>
+        <v>0.04343524575233459</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.001466057728976011</v>
+        <v>0.01566282846033573</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.002253298182040453</v>
+        <v>0.1152316629886627</v>
       </c>
       <c r="CZ17" t="n">
-        <v>6.65863772155717e-05</v>
+        <v>0.01676870137453079</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.001439173240214586</v>
+        <v>0.02944963425397873</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.000771836144849658</v>
+        <v>0.008272305130958557</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0004294119426049292</v>
+        <v>0.03011217154562473</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.446739330887794e-05</v>
+        <v>0.004129620268940926</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0006168020190671086</v>
+        <v>0.01995382830500603</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.00396361481398344</v>
+        <v>0.08755848556756973</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.670326987048611e-05</v>
+        <v>0.05755960568785667</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.008079413324594498</v>
+        <v>0.08276443183422089</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.001062733819708228</v>
+        <v>0.07618886977434158</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.002709171269088984</v>
+        <v>0.03861147537827492</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.001673477119766176</v>
+        <v>0.02356577292084694</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.00091331492876634</v>
+        <v>0.1406819522380829</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.000556513958144933</v>
+        <v>0.03373050689697266</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.000999729847535491</v>
+        <v>0.03457430750131607</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0007981607923284173</v>
+        <v>0.0400700606405735</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0002295806189067662</v>
+        <v>0.01675908826291561</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.001036558533087373</v>
+        <v>0.04540922492742538</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.001763200736604631</v>
+        <v>0.006643909960985184</v>
       </c>
       <c r="DS17" t="n">
-        <v>7.070397259667516e-05</v>
+        <v>0.03905768319964409</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.001410309574566782</v>
+        <v>0.03451887518167496</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.001362343900837004</v>
+        <v>0.03713445737957954</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.0016501973150298</v>
+        <v>0.08047015219926834</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0001983006513910368</v>
+        <v>0.04034887999296188</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0005868833977729082</v>
+        <v>0.004967594519257545</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.001079747220501304</v>
+        <v>0.02407044917345047</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.001121436478570104</v>
+        <v>0.02067679911851883</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.002436260227113962</v>
+        <v>0.03172700852155685</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.001276994240470231</v>
+        <v>0.04921852052211761</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.00056366843637079</v>
+        <v>0.0159965455532074</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0007105825352482498</v>
+        <v>0.1234158799052238</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0007818184676580131</v>
+        <v>0.06755369156599045</v>
       </c>
       <c r="EF17" t="n">
-        <v>2.009968739002943e-05</v>
+        <v>0.02777727693319321</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.002017669146880507</v>
+        <v>0.04377686977386475</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.001435866812244058</v>
+        <v>0.01084759458899498</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.001352780032902956</v>
+        <v>0.09977306425571442</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.001933492487296462</v>
+        <v>0.02663696743547916</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.001816855743527412</v>
+        <v>0.02139769122004509</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0008675493882037699</v>
+        <v>0.005873296409845352</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0001863570214482024</v>
+        <v>0.03709248453378677</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0002324947708984837</v>
+        <v>0.0124597642570734</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0002705066581256688</v>
+        <v>0.004755999892950058</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0009475532569922507</v>
+        <v>0.02786604315042496</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.00266963173635304</v>
+        <v>0.01449777279049158</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.001272860914468765</v>
+        <v>0.07964864373207092</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0002029549214057624</v>
+        <v>0.02668851986527443</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.002799508860334754</v>
+        <v>0.02778097800910473</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.001202836632728577</v>
+        <v>0.04494814202189445</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.001704782014712691</v>
+        <v>0.02085910737514496</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0001169858587672934</v>
+        <v>0.06687431037425995</v>
       </c>
       <c r="EX17" t="n">
-        <v>9.429760393686593e-05</v>
+        <v>0.01603112928569317</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.002387701068073511</v>
+        <v>0.05931233242154121</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.001094709034077823</v>
+        <v>0.01066383626312017</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.002542849397286773</v>
+        <v>0.1255294382572174</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0004850226687267423</v>
+        <v>0.008160490542650223</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.001409980235621333</v>
+        <v>0.01028208434581757</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.001037256559357047</v>
+        <v>0.01479725819081068</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0003357979585416615</v>
+        <v>0.0355745330452919</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0006386686582118273</v>
+        <v>0.008850537240505219</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0005269662942737341</v>
+        <v>0.01519791129976511</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.001700358232483268</v>
+        <v>0.03379688411951065</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.001148008974269032</v>
+        <v>0.001569801010191441</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.002053787931799889</v>
+        <v>0.06678348034620285</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.001084404299035668</v>
+        <v>0.01276491954922676</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.001238456112332642</v>
+        <v>0.008089793846011162</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0003878040297422558</v>
+        <v>0.0005286158993840218</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0003439640568103641</v>
+        <v>0.02517411857843399</v>
       </c>
       <c r="FO17" t="n">
-        <v>4.146212449995801e-05</v>
+        <v>0.02645938470959663</v>
       </c>
       <c r="FP17" t="n">
-        <v>6.564334034919739e-05</v>
+        <v>0.02643405459821224</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.002409696113318205</v>
+        <v>0.0220540352165699</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.003435387741774321</v>
+        <v>0.008430066518485546</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.001916344510391355</v>
+        <v>0.09339997172355652</v>
       </c>
       <c r="FT17" t="n">
-        <v>7.169050513766706e-05</v>
+        <v>0.09555686265230179</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.002304274821653962</v>
+        <v>0.0487205982208252</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.001308309729211032</v>
+        <v>0.00766422413289547</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0005038888775743544</v>
+        <v>0.09920606017112732</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0005846074782311916</v>
+        <v>0.0005758120678365231</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.002582433633506298</v>
+        <v>0.06988377124071121</v>
       </c>
       <c r="FZ17" t="n">
-        <v>9.999338362831622e-05</v>
+        <v>0.08561310917139053</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.001161291846074164</v>
+        <v>0.050982765853405</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.001075188396498561</v>
+        <v>0.07156100869178772</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0001161110631073825</v>
+        <v>0.07390869408845901</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.002734127687290311</v>
+        <v>0.03086531721055508</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.007577483542263508</v>
+        <v>0.1160277724266052</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.001384860835969448</v>
+        <v>0.006431094370782375</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0006469401414506137</v>
+        <v>0.03753187134861946</v>
       </c>
     </row>
   </sheetData>
